--- a/excel/云下/订单.xlsx
+++ b/excel/云下/订单.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="588">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="592">
   <si>
     <t/>
   </si>
@@ -1786,6 +1786,18 @@
   <si>
     <t>1桶=6000g</t>
   </si>
+  <si>
+    <t>丘北干辣椒细面）</t>
+  </si>
+  <si>
+    <t>沙拉碗（云下500ml）</t>
+  </si>
+  <si>
+    <t>沙拉碗（云下1000ml）</t>
+  </si>
+  <si>
+    <t>丘北干辣椒（细面）</t>
+  </si>
 </sst>
 </file>
 
@@ -3099,7 +3111,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="Z1138"/>
+  <dimension ref="Z1137"/>
   <sheetFormatPr defaultColWidth="9.55752" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="23.1416" style="62" customWidth="1"/>
@@ -3245,7 +3257,7 @@
       <c r="D4" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>26</v>
       </c>
       <c r="F4" s="4">
@@ -4663,7 +4675,7 @@
       <c r="D41" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E41" s="4" t="s">
+      <c r="E41" s="5" t="s">
         <v>26</v>
       </c>
       <c r="F41" s="4">
@@ -4929,8 +4941,8 @@
       <c r="D48" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E48" s="4" t="s">
-        <v>58</v>
+      <c r="E48" s="60" t="s">
+        <v>591</v>
       </c>
       <c r="F48" s="4">
         <v>1.2</v>
@@ -5464,8 +5476,8 @@
       <c r="D62" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E62" s="4" t="s">
-        <v>60</v>
+      <c r="E62" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="F62" s="4">
         <v>1</v>
@@ -6037,8 +6049,8 @@
       <c r="D77" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E77" s="4" t="s">
-        <v>58</v>
+      <c r="E77" s="60" t="s">
+        <v>591</v>
       </c>
       <c r="F77" s="4">
         <v>1</v>
@@ -8782,8 +8794,8 @@
       <c r="D149" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E149" s="4" t="s">
-        <v>60</v>
+      <c r="E149" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="F149" s="4">
         <v>1</v>
@@ -26730,8 +26742,8 @@
       <c r="D621" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E621" s="4" t="s">
-        <v>169</v>
+      <c r="E621" s="5" t="s">
+        <v>465</v>
       </c>
       <c r="F621" s="4">
         <v>2</v>
@@ -29656,8 +29668,8 @@
       <c r="D698" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E698" s="4" t="s">
-        <v>169</v>
+      <c r="E698" s="5" t="s">
+        <v>465</v>
       </c>
       <c r="F698" s="4">
         <v>1</v>
@@ -35471,22 +35483,22 @@
         <v>70</v>
       </c>
       <c r="E851" s="4" t="s">
-        <v>183</v>
+        <v>74</v>
       </c>
       <c r="F851" s="4">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G851" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H851" s="4">
-        <v>12.5</v>
+        <v>4</v>
       </c>
       <c r="I851" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J851" s="4">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K851" s="4" t="s">
         <v>25</v>
@@ -35506,25 +35518,25 @@
         <v>14</v>
       </c>
       <c r="D852" s="4" t="s">
-        <v>70</v>
+        <v>154</v>
       </c>
       <c r="E852" s="4" t="s">
-        <v>74</v>
+        <v>155</v>
       </c>
       <c r="F852" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G852" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H852" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I852" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J852" s="4">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="K852" s="4" t="s">
         <v>25</v>
@@ -35544,25 +35556,25 @@
         <v>14</v>
       </c>
       <c r="D853" s="4" t="s">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="E853" s="4" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="F853" s="4">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="G853" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H853" s="4">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="I853" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J853" s="4">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="K853" s="4" t="s">
         <v>25</v>
@@ -35585,22 +35597,22 @@
         <v>76</v>
       </c>
       <c r="E854" s="4" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="F854" s="4">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="G854" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H854" s="4">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="I854" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J854" s="4">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="K854" s="4" t="s">
         <v>25</v>
@@ -35623,7 +35635,7 @@
         <v>76</v>
       </c>
       <c r="E855" s="4" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="F855" s="4">
         <v>1</v>
@@ -35632,13 +35644,13 @@
         <v>17</v>
       </c>
       <c r="H855" s="4">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I855" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J855" s="4">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="K855" s="4" t="s">
         <v>25</v>
@@ -35661,7 +35673,7 @@
         <v>76</v>
       </c>
       <c r="E856" s="4" t="s">
-        <v>104</v>
+        <v>133</v>
       </c>
       <c r="F856" s="4">
         <v>1</v>
@@ -35670,13 +35682,13 @@
         <v>17</v>
       </c>
       <c r="H856" s="4">
-        <v>17</v>
+        <v>8.5</v>
       </c>
       <c r="I856" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J856" s="4">
-        <v>17</v>
+        <v>8.5</v>
       </c>
       <c r="K856" s="4" t="s">
         <v>25</v>
@@ -35699,7 +35711,7 @@
         <v>76</v>
       </c>
       <c r="E857" s="4" t="s">
-        <v>133</v>
+        <v>82</v>
       </c>
       <c r="F857" s="4">
         <v>1</v>
@@ -35708,13 +35720,13 @@
         <v>17</v>
       </c>
       <c r="H857" s="4">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="I857" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J857" s="4">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="K857" s="4" t="s">
         <v>25</v>
@@ -35737,22 +35749,22 @@
         <v>76</v>
       </c>
       <c r="E858" s="4" t="s">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="F858" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G858" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="H858" s="4">
         <v>5.5</v>
       </c>
       <c r="I858" s="4" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="J858" s="4">
-        <v>5.5</v>
+        <v>11</v>
       </c>
       <c r="K858" s="4" t="s">
         <v>25</v>
@@ -35775,22 +35787,22 @@
         <v>76</v>
       </c>
       <c r="E859" s="4" t="s">
-        <v>135</v>
+        <v>85</v>
       </c>
       <c r="F859" s="4">
         <v>2</v>
       </c>
       <c r="G859" s="4" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="H859" s="4">
-        <v>5.5</v>
+        <v>7.63</v>
       </c>
       <c r="I859" s="4" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="J859" s="4">
-        <v>11</v>
+        <v>15.26</v>
       </c>
       <c r="K859" s="4" t="s">
         <v>25</v>
@@ -35813,22 +35825,22 @@
         <v>76</v>
       </c>
       <c r="E860" s="4" t="s">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="F860" s="4">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="G860" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H860" s="4">
-        <v>7.63</v>
+        <v>20</v>
       </c>
       <c r="I860" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J860" s="4">
-        <v>15.26</v>
+        <v>4</v>
       </c>
       <c r="K860" s="4" t="s">
         <v>25</v>
@@ -35851,22 +35863,22 @@
         <v>76</v>
       </c>
       <c r="E861" s="4" t="s">
-        <v>128</v>
+        <v>87</v>
       </c>
       <c r="F861" s="4">
-        <v>0.2</v>
+        <v>8</v>
       </c>
       <c r="G861" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H861" s="4">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="I861" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J861" s="4">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="K861" s="4" t="s">
         <v>25</v>
@@ -35889,22 +35901,22 @@
         <v>76</v>
       </c>
       <c r="E862" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F862" s="4">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G862" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H862" s="4">
-        <v>3</v>
+        <v>6.8</v>
       </c>
       <c r="I862" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J862" s="4">
-        <v>24</v>
+        <v>20.4</v>
       </c>
       <c r="K862" s="4" t="s">
         <v>25</v>
@@ -35927,22 +35939,22 @@
         <v>76</v>
       </c>
       <c r="E863" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F863" s="4">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G863" s="4" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="H863" s="4">
-        <v>6.8</v>
+        <v>2.5</v>
       </c>
       <c r="I863" s="4" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="J863" s="4">
-        <v>20.4</v>
+        <v>30</v>
       </c>
       <c r="K863" s="4" t="s">
         <v>25</v>
@@ -35965,22 +35977,22 @@
         <v>76</v>
       </c>
       <c r="E864" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F864" s="4">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G864" s="4" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="H864" s="4">
-        <v>2.5</v>
+        <v>8.5</v>
       </c>
       <c r="I864" s="4" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="J864" s="4">
-        <v>30</v>
+        <v>8.5</v>
       </c>
       <c r="K864" s="4" t="s">
         <v>25</v>
@@ -36003,22 +36015,22 @@
         <v>76</v>
       </c>
       <c r="E865" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F865" s="4">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G865" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H865" s="4">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="I865" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J865" s="4">
-        <v>8.5</v>
+        <v>6.4</v>
       </c>
       <c r="K865" s="4" t="s">
         <v>25</v>
@@ -36041,22 +36053,22 @@
         <v>76</v>
       </c>
       <c r="E866" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F866" s="4">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="G866" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H866" s="4">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="I866" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J866" s="4">
-        <v>6.4</v>
+        <v>28.5</v>
       </c>
       <c r="K866" s="4" t="s">
         <v>25</v>
@@ -36076,25 +36088,25 @@
         <v>14</v>
       </c>
       <c r="D867" s="4" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="E867" s="4" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="F867" s="4">
-        <v>3</v>
+        <v>10.6</v>
       </c>
       <c r="G867" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H867" s="4">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="I867" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J867" s="4">
-        <v>28.5</v>
+        <v>53</v>
       </c>
       <c r="K867" s="4" t="s">
         <v>25</v>
@@ -36117,22 +36129,22 @@
         <v>97</v>
       </c>
       <c r="E868" s="4" t="s">
-        <v>99</v>
+        <v>147</v>
       </c>
       <c r="F868" s="4">
-        <v>10.6</v>
+        <v>1.4</v>
       </c>
       <c r="G868" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H868" s="4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I868" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J868" s="4">
-        <v>53</v>
+        <v>5.6</v>
       </c>
       <c r="K868" s="4" t="s">
         <v>25</v>
@@ -36155,22 +36167,22 @@
         <v>97</v>
       </c>
       <c r="E869" s="4" t="s">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="F869" s="4">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="G869" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H869" s="4">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="I869" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J869" s="4">
-        <v>5.6</v>
+        <v>6.5</v>
       </c>
       <c r="K869" s="4" t="s">
         <v>25</v>
@@ -36184,31 +36196,31 @@
         <v>69</v>
       </c>
       <c r="B870" s="6">
-        <v>46133</v>
+        <v>46136</v>
       </c>
       <c r="C870" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D870" s="4" t="s">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="E870" s="4" t="s">
-        <v>170</v>
+        <v>72</v>
       </c>
       <c r="F870" s="4">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="G870" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H870" s="4">
-        <v>6.5</v>
+        <v>11.5</v>
       </c>
       <c r="I870" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J870" s="4">
-        <v>6.5</v>
+        <v>632.5</v>
       </c>
       <c r="K870" s="4" t="s">
         <v>25</v>
@@ -36231,22 +36243,22 @@
         <v>70</v>
       </c>
       <c r="E871" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F871" s="4">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="G871" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H871" s="4">
-        <v>11.5</v>
+        <v>4</v>
       </c>
       <c r="I871" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J871" s="4">
-        <v>632.5</v>
+        <v>20</v>
       </c>
       <c r="K871" s="4" t="s">
         <v>25</v>
@@ -36269,22 +36281,22 @@
         <v>70</v>
       </c>
       <c r="E872" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F872" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G872" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H872" s="4">
-        <v>4</v>
+        <v>13.8</v>
       </c>
       <c r="I872" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J872" s="4">
-        <v>20</v>
+        <v>82.8</v>
       </c>
       <c r="K872" s="4" t="s">
         <v>25</v>
@@ -36304,25 +36316,25 @@
         <v>14</v>
       </c>
       <c r="D873" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E873" s="4" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="F873" s="4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G873" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H873" s="4">
-        <v>13.8</v>
+        <v>4.5</v>
       </c>
       <c r="I873" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J873" s="4">
-        <v>82.8</v>
+        <v>4.5</v>
       </c>
       <c r="K873" s="4" t="s">
         <v>25</v>
@@ -36345,22 +36357,22 @@
         <v>76</v>
       </c>
       <c r="E874" s="4" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="F874" s="4">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="G874" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H874" s="4">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="I874" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J874" s="4">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="K874" s="4" t="s">
         <v>25</v>
@@ -36383,22 +36395,22 @@
         <v>76</v>
       </c>
       <c r="E875" s="4" t="s">
-        <v>112</v>
+        <v>149</v>
       </c>
       <c r="F875" s="4">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="G875" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H875" s="4">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="I875" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J875" s="4">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="K875" s="4" t="s">
         <v>25</v>
@@ -36421,22 +36433,22 @@
         <v>76</v>
       </c>
       <c r="E876" s="4" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="F876" s="4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G876" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H876" s="4">
-        <v>18</v>
+        <v>8.5</v>
       </c>
       <c r="I876" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J876" s="4">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="K876" s="4" t="s">
         <v>25</v>
@@ -36459,7 +36471,7 @@
         <v>76</v>
       </c>
       <c r="E877" s="4" t="s">
-        <v>133</v>
+        <v>114</v>
       </c>
       <c r="F877" s="4">
         <v>1</v>
@@ -36497,22 +36509,22 @@
         <v>76</v>
       </c>
       <c r="E878" s="4" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="F878" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G878" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H878" s="4">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="I878" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J878" s="4">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="K878" s="4" t="s">
         <v>25</v>
@@ -36535,22 +36547,22 @@
         <v>76</v>
       </c>
       <c r="E879" s="4" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="F879" s="4">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="G879" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H879" s="4">
-        <v>5.5</v>
+        <v>20</v>
       </c>
       <c r="I879" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J879" s="4">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="K879" s="4" t="s">
         <v>25</v>
@@ -36573,22 +36585,22 @@
         <v>76</v>
       </c>
       <c r="E880" s="4" t="s">
-        <v>115</v>
+        <v>83</v>
       </c>
       <c r="F880" s="4">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="G880" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H880" s="4">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I880" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J880" s="4">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="K880" s="4" t="s">
         <v>25</v>
@@ -36611,10 +36623,10 @@
         <v>76</v>
       </c>
       <c r="E881" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F881" s="4">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G881" s="4" t="s">
         <v>17</v>
@@ -36626,7 +36638,7 @@
         <v>18</v>
       </c>
       <c r="J881" s="4">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="K881" s="4" t="s">
         <v>25</v>
@@ -36649,22 +36661,22 @@
         <v>76</v>
       </c>
       <c r="E882" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F882" s="4">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="G882" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H882" s="4">
-        <v>18</v>
+        <v>7.63</v>
       </c>
       <c r="I882" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J882" s="4">
-        <v>9</v>
+        <v>15.26</v>
       </c>
       <c r="K882" s="4" t="s">
         <v>25</v>
@@ -36687,22 +36699,22 @@
         <v>76</v>
       </c>
       <c r="E883" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F883" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G883" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H883" s="4">
-        <v>7.63</v>
+        <v>7</v>
       </c>
       <c r="I883" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J883" s="4">
-        <v>15.26</v>
+        <v>35</v>
       </c>
       <c r="K883" s="4" t="s">
         <v>25</v>
@@ -36725,22 +36737,22 @@
         <v>76</v>
       </c>
       <c r="E884" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F884" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G884" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H884" s="4">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I884" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J884" s="4">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K884" s="4" t="s">
         <v>25</v>
@@ -36763,22 +36775,22 @@
         <v>76</v>
       </c>
       <c r="E885" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F885" s="4">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G885" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H885" s="4">
-        <v>3</v>
+        <v>6.8</v>
       </c>
       <c r="I885" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J885" s="4">
-        <v>30</v>
+        <v>20.4</v>
       </c>
       <c r="K885" s="4" t="s">
         <v>25</v>
@@ -36801,22 +36813,22 @@
         <v>76</v>
       </c>
       <c r="E886" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F886" s="4">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G886" s="4" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="H886" s="4">
-        <v>6.8</v>
+        <v>2.5</v>
       </c>
       <c r="I886" s="4" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="J886" s="4">
-        <v>20.4</v>
+        <v>37.5</v>
       </c>
       <c r="K886" s="4" t="s">
         <v>25</v>
@@ -36839,22 +36851,22 @@
         <v>76</v>
       </c>
       <c r="E887" s="4" t="s">
-        <v>89</v>
+        <v>129</v>
       </c>
       <c r="F887" s="4">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="G887" s="4" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="H887" s="4">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="I887" s="4" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="J887" s="4">
-        <v>37.5</v>
+        <v>7</v>
       </c>
       <c r="K887" s="4" t="s">
         <v>25</v>
@@ -36877,22 +36889,22 @@
         <v>76</v>
       </c>
       <c r="E888" s="4" t="s">
-        <v>129</v>
+        <v>90</v>
       </c>
       <c r="F888" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G888" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H888" s="4">
-        <v>3.5</v>
+        <v>8.5</v>
       </c>
       <c r="I888" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J888" s="4">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="K888" s="4" t="s">
         <v>25</v>
@@ -36915,7 +36927,7 @@
         <v>76</v>
       </c>
       <c r="E889" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F889" s="4">
         <v>1</v>
@@ -36924,13 +36936,13 @@
         <v>17</v>
       </c>
       <c r="H889" s="4">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="I889" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J889" s="4">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="K889" s="4" t="s">
         <v>25</v>
@@ -36953,22 +36965,22 @@
         <v>76</v>
       </c>
       <c r="E890" s="4" t="s">
-        <v>91</v>
+        <v>107</v>
       </c>
       <c r="F890" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G890" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H890" s="4">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I890" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J890" s="4">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K890" s="4" t="s">
         <v>25</v>
@@ -36991,22 +37003,22 @@
         <v>76</v>
       </c>
       <c r="E891" s="4" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="F891" s="4">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G891" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H891" s="4">
-        <v>2</v>
+        <v>9.5</v>
       </c>
       <c r="I891" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J891" s="4">
-        <v>10</v>
+        <v>28.5</v>
       </c>
       <c r="K891" s="4" t="s">
         <v>25</v>
@@ -37029,22 +37041,22 @@
         <v>76</v>
       </c>
       <c r="E892" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F892" s="4">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="G892" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H892" s="4">
-        <v>9.5</v>
+        <v>2.5</v>
       </c>
       <c r="I892" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J892" s="4">
-        <v>28.5</v>
+        <v>100</v>
       </c>
       <c r="K892" s="4" t="s">
         <v>25</v>
@@ -37064,25 +37076,25 @@
         <v>14</v>
       </c>
       <c r="D893" s="4" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="E893" s="4" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="F893" s="4">
+        <v>4</v>
+      </c>
+      <c r="G893" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="H893" s="4">
+        <v>10</v>
+      </c>
+      <c r="I893" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="J893" s="4">
         <v>40</v>
-      </c>
-      <c r="G893" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H893" s="4">
-        <v>2.5</v>
-      </c>
-      <c r="I893" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J893" s="4">
-        <v>100</v>
       </c>
       <c r="K893" s="4" t="s">
         <v>25</v>
@@ -37105,22 +37117,22 @@
         <v>97</v>
       </c>
       <c r="E894" s="4" t="s">
-        <v>102</v>
+        <v>170</v>
       </c>
       <c r="F894" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G894" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H894" s="4">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="I894" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J894" s="4">
-        <v>40</v>
+        <v>6.5</v>
       </c>
       <c r="K894" s="4" t="s">
         <v>25</v>
@@ -37143,10 +37155,10 @@
         <v>97</v>
       </c>
       <c r="E895" s="4" t="s">
-        <v>170</v>
+        <v>98</v>
       </c>
       <c r="F895" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G895" s="4" t="s">
         <v>17</v>
@@ -37158,7 +37170,7 @@
         <v>18</v>
       </c>
       <c r="J895" s="4">
-        <v>6.5</v>
+        <v>39</v>
       </c>
       <c r="K895" s="4" t="s">
         <v>25</v>
@@ -37178,25 +37190,25 @@
         <v>14</v>
       </c>
       <c r="D896" s="4" t="s">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="E896" s="4" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="F896" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G896" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H896" s="4">
-        <v>6.5</v>
+        <v>18</v>
       </c>
       <c r="I896" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J896" s="4">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="K896" s="4" t="s">
         <v>25</v>
@@ -37218,23 +37230,23 @@
       <c r="D897" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E897" s="4" t="s">
-        <v>73</v>
+      <c r="E897" s="60" t="s">
+        <v>165</v>
       </c>
       <c r="F897" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G897" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H897" s="4">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="I897" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J897" s="4">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K897" s="4" t="s">
         <v>25</v>
@@ -37248,7 +37260,7 @@
         <v>69</v>
       </c>
       <c r="B898" s="6">
-        <v>46136</v>
+        <v>46134</v>
       </c>
       <c r="C898" s="4" t="s">
         <v>14</v>
@@ -37256,23 +37268,23 @@
       <c r="D898" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="E898" s="60" t="s">
-        <v>165</v>
+      <c r="E898" s="4" t="s">
+        <v>73</v>
       </c>
       <c r="F898" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G898" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H898" s="4">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="I898" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J898" s="4">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="K898" s="4" t="s">
         <v>25</v>
@@ -37295,22 +37307,22 @@
         <v>70</v>
       </c>
       <c r="E899" s="4" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="F899" s="4">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G899" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H899" s="4">
-        <v>18</v>
+        <v>12.5</v>
       </c>
       <c r="I899" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J899" s="4">
-        <v>72</v>
+        <v>125</v>
       </c>
       <c r="K899" s="4" t="s">
         <v>25</v>
@@ -37333,22 +37345,22 @@
         <v>70</v>
       </c>
       <c r="E900" s="4" t="s">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="F900" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G900" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H900" s="4">
-        <v>12.5</v>
+        <v>4</v>
       </c>
       <c r="I900" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J900" s="4">
-        <v>125</v>
+        <v>20</v>
       </c>
       <c r="K900" s="4" t="s">
         <v>25</v>
@@ -37371,22 +37383,22 @@
         <v>70</v>
       </c>
       <c r="E901" s="4" t="s">
-        <v>74</v>
+        <v>141</v>
       </c>
       <c r="F901" s="4">
-        <v>5</v>
+        <v>1.1</v>
       </c>
       <c r="G901" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H901" s="4">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="I901" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J901" s="4">
-        <v>20</v>
+        <v>30.8</v>
       </c>
       <c r="K901" s="4" t="s">
         <v>25</v>
@@ -37409,22 +37421,22 @@
         <v>70</v>
       </c>
       <c r="E902" s="4" t="s">
-        <v>141</v>
+        <v>75</v>
       </c>
       <c r="F902" s="4">
-        <v>1.1</v>
+        <v>4</v>
       </c>
       <c r="G902" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H902" s="4">
-        <v>28</v>
+        <v>13.8</v>
       </c>
       <c r="I902" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J902" s="4">
-        <v>30.8</v>
+        <v>55.2</v>
       </c>
       <c r="K902" s="4" t="s">
         <v>25</v>
@@ -37444,25 +37456,25 @@
         <v>14</v>
       </c>
       <c r="D903" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E903" s="4" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="F903" s="4">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="G903" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H903" s="4">
-        <v>13.8</v>
+        <v>2.5</v>
       </c>
       <c r="I903" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J903" s="4">
-        <v>55.2</v>
+        <v>50</v>
       </c>
       <c r="K903" s="4" t="s">
         <v>25</v>
@@ -37485,22 +37497,22 @@
         <v>76</v>
       </c>
       <c r="E904" s="4" t="s">
-        <v>94</v>
+        <v>138</v>
       </c>
       <c r="F904" s="4">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G904" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H904" s="4">
-        <v>2.5</v>
+        <v>20</v>
       </c>
       <c r="I904" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J904" s="4">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K904" s="4" t="s">
         <v>25</v>
@@ -37523,22 +37535,22 @@
         <v>76</v>
       </c>
       <c r="E905" s="4" t="s">
-        <v>138</v>
+        <v>87</v>
       </c>
       <c r="F905" s="4">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G905" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H905" s="4">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="I905" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J905" s="4">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="K905" s="4" t="s">
         <v>25</v>
@@ -37561,22 +37573,22 @@
         <v>76</v>
       </c>
       <c r="E906" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F906" s="4">
+        <v>6</v>
+      </c>
+      <c r="G906" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H906" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="I906" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J906" s="4">
         <v>15</v>
-      </c>
-      <c r="G906" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="H906" s="4">
-        <v>3</v>
-      </c>
-      <c r="I906" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J906" s="4">
-        <v>45</v>
       </c>
       <c r="K906" s="4" t="s">
         <v>25</v>
@@ -37599,22 +37611,22 @@
         <v>76</v>
       </c>
       <c r="E907" s="4" t="s">
-        <v>89</v>
+        <v>129</v>
       </c>
       <c r="F907" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G907" s="4" t="s">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="H907" s="4">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="I907" s="4" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="J907" s="4">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="K907" s="4" t="s">
         <v>25</v>
@@ -37637,22 +37649,22 @@
         <v>76</v>
       </c>
       <c r="E908" s="4" t="s">
-        <v>129</v>
+        <v>78</v>
       </c>
       <c r="F908" s="4">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="G908" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H908" s="4">
-        <v>3.5</v>
+        <v>18</v>
       </c>
       <c r="I908" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J908" s="4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K908" s="4" t="s">
         <v>25</v>
@@ -37675,22 +37687,22 @@
         <v>76</v>
       </c>
       <c r="E909" s="4" t="s">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="F909" s="4">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="G909" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H909" s="4">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="I909" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J909" s="4">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="K909" s="4" t="s">
         <v>25</v>
@@ -37713,7 +37725,7 @@
         <v>76</v>
       </c>
       <c r="E910" s="4" t="s">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="F910" s="4">
         <v>1</v>
@@ -37722,13 +37734,13 @@
         <v>17</v>
       </c>
       <c r="H910" s="4">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="I910" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J910" s="4">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="K910" s="4" t="s">
         <v>25</v>
@@ -37751,7 +37763,7 @@
         <v>76</v>
       </c>
       <c r="E911" s="4" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="F911" s="4">
         <v>1</v>
@@ -37760,13 +37772,13 @@
         <v>17</v>
       </c>
       <c r="H911" s="4">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="I911" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J911" s="4">
-        <v>8.5</v>
+        <v>5.5</v>
       </c>
       <c r="K911" s="4" t="s">
         <v>25</v>
@@ -37789,7 +37801,7 @@
         <v>76</v>
       </c>
       <c r="E912" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F912" s="4">
         <v>1</v>
@@ -37798,13 +37810,13 @@
         <v>17</v>
       </c>
       <c r="H912" s="4">
-        <v>5.5</v>
+        <v>18</v>
       </c>
       <c r="I912" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J912" s="4">
-        <v>5.5</v>
+        <v>18</v>
       </c>
       <c r="K912" s="4" t="s">
         <v>25</v>
@@ -37827,22 +37839,22 @@
         <v>76</v>
       </c>
       <c r="E913" s="4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F913" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G913" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H913" s="4">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="I913" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J913" s="4">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="K913" s="4" t="s">
         <v>25</v>
@@ -37865,22 +37877,22 @@
         <v>76</v>
       </c>
       <c r="E914" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F914" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G914" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H914" s="4">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="I914" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J914" s="4">
-        <v>28</v>
+        <v>20.4</v>
       </c>
       <c r="K914" s="4" t="s">
         <v>25</v>
@@ -37903,22 +37915,22 @@
         <v>76</v>
       </c>
       <c r="E915" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F915" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G915" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H915" s="4">
-        <v>6.8</v>
+        <v>8.5</v>
       </c>
       <c r="I915" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J915" s="4">
-        <v>20.4</v>
+        <v>8.5</v>
       </c>
       <c r="K915" s="4" t="s">
         <v>25</v>
@@ -37941,7 +37953,7 @@
         <v>76</v>
       </c>
       <c r="E916" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F916" s="4">
         <v>1</v>
@@ -37950,13 +37962,13 @@
         <v>17</v>
       </c>
       <c r="H916" s="4">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="I916" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J916" s="4">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="K916" s="4" t="s">
         <v>25</v>
@@ -37979,7 +37991,7 @@
         <v>76</v>
       </c>
       <c r="E917" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F917" s="4">
         <v>1</v>
@@ -37988,13 +38000,13 @@
         <v>17</v>
       </c>
       <c r="H917" s="4">
-        <v>8</v>
+        <v>14.5</v>
       </c>
       <c r="I917" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J917" s="4">
-        <v>8</v>
+        <v>14.5</v>
       </c>
       <c r="K917" s="4" t="s">
         <v>25</v>
@@ -38014,25 +38026,25 @@
         <v>14</v>
       </c>
       <c r="D918" s="4" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="E918" s="4" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="F918" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G918" s="4" t="s">
         <v>17</v>
       </c>
       <c r="H918" s="4">
-        <v>14.5</v>
+        <v>10</v>
       </c>
       <c r="I918" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J918" s="4">
-        <v>14.5</v>
+        <v>50</v>
       </c>
       <c r="K918" s="4" t="s">
         <v>25</v>
@@ -38055,22 +38067,22 @@
         <v>97</v>
       </c>
       <c r="E919" s="4" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="F919" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G919" s="4" t="s">
-        <v>17</v>
+        <v>119</v>
       </c>
       <c r="H919" s="4">
-        <v>10</v>
+        <v>0.7</v>
       </c>
       <c r="I919" s="4" t="s">
-        <v>18</v>
+        <v>120</v>
       </c>
       <c r="J919" s="4">
-        <v>50</v>
+        <v>7</v>
       </c>
       <c r="K919" s="4" t="s">
         <v>25</v>
@@ -38093,22 +38105,22 @@
         <v>97</v>
       </c>
       <c r="E920" s="4" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="F920" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G920" s="4" t="s">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="H920" s="4">
-        <v>0.7</v>
+        <v>4.5</v>
       </c>
       <c r="I920" s="4" t="s">
-        <v>120</v>
+        <v>18</v>
       </c>
       <c r="J920" s="4">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="K920" s="4" t="s">
         <v>25</v>
@@ -38128,10 +38140,10 @@
         <v>14</v>
       </c>
       <c r="D921" s="4" t="s">
-        <v>97</v>
+        <v>70</v>
       </c>
       <c r="E921" s="4" t="s">
-        <v>131</v>
+        <v>71</v>
       </c>
       <c r="F921" s="4">
         <v>1</v>
@@ -38140,13 +38152,13 @@
         <v>17</v>
       </c>
       <c r="H921" s="4">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="I921" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J921" s="4">
-        <v>4.5</v>
+        <v>14.5</v>
       </c>
       <c r="K921" s="4" t="s">
         <v>25</v>
@@ -38157,37 +38169,37 @@
     </row>
     <row r="922" spans="1:12">
       <c r="A922" s="4" t="s">
-        <v>69</v>
+        <v>185</v>
       </c>
       <c r="B922" s="6">
-        <v>46134</v>
+        <v>46114.702341664</v>
       </c>
       <c r="C922" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D922" s="4" t="s">
-        <v>70</v>
+        <v>154</v>
       </c>
       <c r="E922" s="4" t="s">
-        <v>71</v>
+        <v>186</v>
       </c>
       <c r="F922" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G922" s="4" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="H922" s="4">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="I922" s="4" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="J922" s="4">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="K922" s="4" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="L922" s="4" t="s">
         <v>20</v>
@@ -38204,22 +38216,22 @@
         <v>14</v>
       </c>
       <c r="D923" s="4" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="E923" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F923" s="4">
         <v>0</v>
       </c>
       <c r="G923" s="4" t="s">
-        <v>34</v>
+        <v>188</v>
       </c>
       <c r="H923" s="4">
         <v>0</v>
       </c>
       <c r="I923" s="4" t="s">
-        <v>36</v>
+        <v>189</v>
       </c>
       <c r="J923" s="4">
         <v>0</v>
@@ -38236,34 +38248,34 @@
         <v>185</v>
       </c>
       <c r="B924" s="6">
-        <v>46114.702341664</v>
+        <v>46140</v>
       </c>
       <c r="C924" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D924" s="4" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="E924" s="4" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F924" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G924" s="4" t="s">
         <v>188</v>
       </c>
       <c r="H924" s="4">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="I924" s="4" t="s">
         <v>189</v>
       </c>
       <c r="J924" s="4">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="K924" s="4" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="L924" s="4" t="s">
         <v>20</v>
@@ -38280,25 +38292,25 @@
         <v>14</v>
       </c>
       <c r="D925" s="4" t="s">
-        <v>154</v>
+        <v>95</v>
       </c>
       <c r="E925" s="4" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="F925" s="4">
         <v>1</v>
       </c>
       <c r="G925" s="4" t="s">
-        <v>188</v>
+        <v>34</v>
       </c>
       <c r="H925" s="4">
-        <v>235</v>
+        <v>50</v>
       </c>
       <c r="I925" s="4" t="s">
-        <v>189</v>
+        <v>36</v>
       </c>
       <c r="J925" s="4">
-        <v>235</v>
+        <v>50</v>
       </c>
       <c r="K925" s="4" t="s">
         <v>25</v>
@@ -38318,25 +38330,25 @@
         <v>14</v>
       </c>
       <c r="D926" s="4" t="s">
-        <v>95</v>
+        <v>154</v>
       </c>
       <c r="E926" s="4" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="F926" s="4">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G926" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H926" s="4">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I926" s="4" t="s">
         <v>36</v>
       </c>
       <c r="J926" s="4">
-        <v>50</v>
+        <v>640</v>
       </c>
       <c r="K926" s="4" t="s">
         <v>25</v>
@@ -38356,25 +38368,25 @@
         <v>14</v>
       </c>
       <c r="D927" s="4" t="s">
-        <v>154</v>
+        <v>95</v>
       </c>
       <c r="E927" s="4" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="F927" s="4">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="G927" s="4" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="H927" s="4">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="I927" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="J927" s="4">
-        <v>640</v>
+        <v>23</v>
       </c>
       <c r="K927" s="4" t="s">
         <v>25</v>
@@ -38388,34 +38400,34 @@
         <v>185</v>
       </c>
       <c r="B928" s="6">
-        <v>46140</v>
+        <v>46124.6952198903</v>
       </c>
       <c r="C928" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D928" s="4" t="s">
-        <v>95</v>
+        <v>154</v>
       </c>
       <c r="E928" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F928" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G928" s="4" t="s">
-        <v>23</v>
+        <v>188</v>
       </c>
       <c r="H928" s="4">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="I928" s="4" t="s">
-        <v>24</v>
+        <v>189</v>
       </c>
       <c r="J928" s="4">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K928" s="4" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="L928" s="4" t="s">
         <v>20</v>
@@ -38432,22 +38444,22 @@
         <v>14</v>
       </c>
       <c r="D929" s="4" t="s">
-        <v>154</v>
+        <v>95</v>
       </c>
       <c r="E929" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F929" s="4">
         <v>0</v>
       </c>
       <c r="G929" s="4" t="s">
-        <v>188</v>
+        <v>44</v>
       </c>
       <c r="H929" s="4">
         <v>0</v>
       </c>
       <c r="I929" s="4" t="s">
-        <v>189</v>
+        <v>45</v>
       </c>
       <c r="J929" s="4">
         <v>0</v>
@@ -38464,34 +38476,34 @@
         <v>185</v>
       </c>
       <c r="B930" s="6">
-        <v>46124.6952198903</v>
+        <v>46140</v>
       </c>
       <c r="C930" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D930" s="4" t="s">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="E930" s="4" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="F930" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G930" s="4" t="s">
-        <v>44</v>
+        <v>188</v>
       </c>
       <c r="H930" s="4">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="I930" s="4" t="s">
-        <v>45</v>
+        <v>189</v>
       </c>
       <c r="J930" s="4">
-        <v>0</v>
+        <v>552</v>
       </c>
       <c r="K930" s="4" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="L930" s="4" t="s">
         <v>20</v>
@@ -38502,31 +38514,31 @@
         <v>185</v>
       </c>
       <c r="B931" s="6">
-        <v>46140</v>
+        <v>46121</v>
       </c>
       <c r="C931" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D931" s="4" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="E931" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F931" s="4">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="G931" s="4" t="s">
-        <v>188</v>
+        <v>34</v>
       </c>
       <c r="H931" s="4">
-        <v>276</v>
+        <v>40</v>
       </c>
       <c r="I931" s="4" t="s">
-        <v>189</v>
+        <v>36</v>
       </c>
       <c r="J931" s="4">
-        <v>552</v>
+        <v>640</v>
       </c>
       <c r="K931" s="4" t="s">
         <v>25</v>
@@ -38546,25 +38558,25 @@
         <v>14</v>
       </c>
       <c r="D932" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="E932" s="4" t="s">
-        <v>186</v>
+        <v>95</v>
+      </c>
+      <c r="E932" s="5" t="s">
+        <v>465</v>
       </c>
       <c r="F932" s="4">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G932" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H932" s="4">
-        <v>40</v>
+        <v>87.5</v>
       </c>
       <c r="I932" s="4" t="s">
         <v>36</v>
       </c>
       <c r="J932" s="4">
-        <v>640</v>
+        <v>175</v>
       </c>
       <c r="K932" s="4" t="s">
         <v>25</v>
@@ -38584,25 +38596,25 @@
         <v>14</v>
       </c>
       <c r="D933" s="4" t="s">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="E933" s="4" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="F933" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G933" s="4" t="s">
-        <v>34</v>
+        <v>188</v>
       </c>
       <c r="H933" s="4">
-        <v>87.5</v>
+        <v>276</v>
       </c>
       <c r="I933" s="4" t="s">
-        <v>36</v>
+        <v>189</v>
       </c>
       <c r="J933" s="4">
-        <v>175</v>
+        <v>276</v>
       </c>
       <c r="K933" s="4" t="s">
         <v>25</v>
@@ -38622,10 +38634,10 @@
         <v>14</v>
       </c>
       <c r="D934" s="4" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="E934" s="4" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="F934" s="4">
         <v>1</v>
@@ -38634,13 +38646,13 @@
         <v>188</v>
       </c>
       <c r="H934" s="4">
-        <v>276</v>
+        <v>300</v>
       </c>
       <c r="I934" s="4" t="s">
         <v>189</v>
       </c>
       <c r="J934" s="4">
-        <v>276</v>
+        <v>300</v>
       </c>
       <c r="K934" s="4" t="s">
         <v>25</v>
@@ -38660,10 +38672,10 @@
         <v>14</v>
       </c>
       <c r="D935" s="4" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="E935" s="4" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F935" s="4">
         <v>1</v>
@@ -38672,13 +38684,13 @@
         <v>188</v>
       </c>
       <c r="H935" s="4">
-        <v>300</v>
+        <v>235</v>
       </c>
       <c r="I935" s="4" t="s">
         <v>189</v>
       </c>
       <c r="J935" s="4">
-        <v>300</v>
+        <v>235</v>
       </c>
       <c r="K935" s="4" t="s">
         <v>25</v>
@@ -38698,25 +38710,25 @@
         <v>14</v>
       </c>
       <c r="D936" s="4" t="s">
-        <v>154</v>
+        <v>95</v>
       </c>
       <c r="E936" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F936" s="4">
         <v>1</v>
       </c>
       <c r="G936" s="4" t="s">
-        <v>188</v>
+        <v>44</v>
       </c>
       <c r="H936" s="4">
-        <v>235</v>
+        <v>47.5</v>
       </c>
       <c r="I936" s="4" t="s">
-        <v>189</v>
+        <v>45</v>
       </c>
       <c r="J936" s="4">
-        <v>235</v>
+        <v>47.5</v>
       </c>
       <c r="K936" s="4" t="s">
         <v>25</v>
@@ -38739,22 +38751,22 @@
         <v>95</v>
       </c>
       <c r="E937" s="4" t="s">
-        <v>192</v>
+        <v>176</v>
       </c>
       <c r="F937" s="4">
         <v>1</v>
       </c>
       <c r="G937" s="4" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="H937" s="4">
-        <v>47.5</v>
+        <v>50</v>
       </c>
       <c r="I937" s="4" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="J937" s="4">
-        <v>47.5</v>
+        <v>50</v>
       </c>
       <c r="K937" s="4" t="s">
         <v>25</v>
@@ -38768,31 +38780,31 @@
         <v>185</v>
       </c>
       <c r="B938" s="6">
-        <v>46121</v>
+        <v>46136</v>
       </c>
       <c r="C938" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D938" s="4" t="s">
-        <v>95</v>
+        <v>154</v>
       </c>
       <c r="E938" s="4" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="F938" s="4">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G938" s="4" t="s">
         <v>34</v>
       </c>
       <c r="H938" s="4">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I938" s="4" t="s">
         <v>36</v>
       </c>
       <c r="J938" s="4">
-        <v>50</v>
+        <v>640</v>
       </c>
       <c r="K938" s="4" t="s">
         <v>25</v>
@@ -38812,25 +38824,25 @@
         <v>14</v>
       </c>
       <c r="D939" s="4" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="E939" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F939" s="4">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="G939" s="4" t="s">
-        <v>34</v>
+        <v>188</v>
       </c>
       <c r="H939" s="4">
-        <v>40</v>
+        <v>276</v>
       </c>
       <c r="I939" s="4" t="s">
-        <v>36</v>
+        <v>189</v>
       </c>
       <c r="J939" s="4">
-        <v>640</v>
+        <v>276</v>
       </c>
       <c r="K939" s="4" t="s">
         <v>25</v>
@@ -38850,10 +38862,10 @@
         <v>14</v>
       </c>
       <c r="D940" s="4" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="E940" s="4" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="F940" s="4">
         <v>1</v>
@@ -38862,13 +38874,13 @@
         <v>188</v>
       </c>
       <c r="H940" s="4">
-        <v>276</v>
+        <v>95</v>
       </c>
       <c r="I940" s="4" t="s">
         <v>189</v>
       </c>
       <c r="J940" s="4">
-        <v>276</v>
+        <v>95</v>
       </c>
       <c r="K940" s="4" t="s">
         <v>25</v>
@@ -38882,31 +38894,31 @@
         <v>185</v>
       </c>
       <c r="B941" s="6">
-        <v>46136</v>
+        <v>46113</v>
       </c>
       <c r="C941" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D941" s="4" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="E941" s="4" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="F941" s="4">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="G941" s="4" t="s">
-        <v>188</v>
+        <v>34</v>
       </c>
       <c r="H941" s="4">
-        <v>95</v>
+        <v>40</v>
       </c>
       <c r="I941" s="4" t="s">
-        <v>189</v>
+        <v>36</v>
       </c>
       <c r="J941" s="4">
-        <v>95</v>
+        <v>1280</v>
       </c>
       <c r="K941" s="4" t="s">
         <v>25</v>
@@ -38926,25 +38938,25 @@
         <v>14</v>
       </c>
       <c r="D942" s="4" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="E942" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F942" s="4">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="G942" s="4" t="s">
-        <v>34</v>
+        <v>188</v>
       </c>
       <c r="H942" s="4">
-        <v>40</v>
+        <v>276</v>
       </c>
       <c r="I942" s="4" t="s">
-        <v>36</v>
+        <v>189</v>
       </c>
       <c r="J942" s="4">
-        <v>1280</v>
+        <v>552</v>
       </c>
       <c r="K942" s="4" t="s">
         <v>25</v>
@@ -38964,25 +38976,25 @@
         <v>14</v>
       </c>
       <c r="D943" s="4" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="E943" s="4" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="F943" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G943" s="4" t="s">
         <v>188</v>
       </c>
       <c r="H943" s="4">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="I943" s="4" t="s">
         <v>189</v>
       </c>
       <c r="J943" s="4">
-        <v>552</v>
+        <v>0</v>
       </c>
       <c r="K943" s="4" t="s">
         <v>25</v>
@@ -39005,22 +39017,22 @@
         <v>164</v>
       </c>
       <c r="E944" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F944" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G944" s="4" t="s">
         <v>188</v>
       </c>
       <c r="H944" s="4">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="I944" s="4" t="s">
         <v>189</v>
       </c>
       <c r="J944" s="4">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="K944" s="4" t="s">
         <v>25</v>
@@ -39043,7 +39055,7 @@
         <v>164</v>
       </c>
       <c r="E945" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F945" s="4">
         <v>1</v>
@@ -39052,13 +39064,13 @@
         <v>188</v>
       </c>
       <c r="H945" s="4">
-        <v>95</v>
+        <v>300</v>
       </c>
       <c r="I945" s="4" t="s">
         <v>189</v>
       </c>
       <c r="J945" s="4">
-        <v>95</v>
+        <v>300</v>
       </c>
       <c r="K945" s="4" t="s">
         <v>25</v>
@@ -39081,7 +39093,7 @@
         <v>164</v>
       </c>
       <c r="E946" s="4" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F946" s="4">
         <v>1</v>
@@ -39090,13 +39102,13 @@
         <v>188</v>
       </c>
       <c r="H946" s="4">
-        <v>300</v>
+        <v>405</v>
       </c>
       <c r="I946" s="4" t="s">
         <v>189</v>
       </c>
       <c r="J946" s="4">
-        <v>300</v>
+        <v>405</v>
       </c>
       <c r="K946" s="4" t="s">
         <v>25</v>
@@ -39110,31 +39122,31 @@
         <v>185</v>
       </c>
       <c r="B947" s="6">
-        <v>46113</v>
+        <v>46129</v>
       </c>
       <c r="C947" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D947" s="4" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="E947" s="4" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="F947" s="4">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G947" s="4" t="s">
-        <v>188</v>
+        <v>34</v>
       </c>
       <c r="H947" s="4">
-        <v>405</v>
+        <v>40</v>
       </c>
       <c r="I947" s="4" t="s">
-        <v>189</v>
+        <v>36</v>
       </c>
       <c r="J947" s="4">
-        <v>405</v>
+        <v>640</v>
       </c>
       <c r="K947" s="4" t="s">
         <v>25</v>
@@ -39154,25 +39166,25 @@
         <v>14</v>
       </c>
       <c r="D948" s="4" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="E948" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F948" s="4">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G948" s="4" t="s">
-        <v>34</v>
+        <v>188</v>
       </c>
       <c r="H948" s="4">
-        <v>40</v>
+        <v>276</v>
       </c>
       <c r="I948" s="4" t="s">
-        <v>36</v>
+        <v>189</v>
       </c>
       <c r="J948" s="4">
-        <v>640</v>
+        <v>552</v>
       </c>
       <c r="K948" s="4" t="s">
         <v>25</v>
@@ -39192,25 +39204,25 @@
         <v>14</v>
       </c>
       <c r="D949" s="4" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="E949" s="4" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="F949" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G949" s="4" t="s">
         <v>188</v>
       </c>
       <c r="H949" s="4">
-        <v>276</v>
+        <v>95</v>
       </c>
       <c r="I949" s="4" t="s">
         <v>189</v>
       </c>
       <c r="J949" s="4">
-        <v>552</v>
+        <v>0</v>
       </c>
       <c r="K949" s="4" t="s">
         <v>25</v>
@@ -39233,22 +39245,22 @@
         <v>164</v>
       </c>
       <c r="E950" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F950" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G950" s="4" t="s">
         <v>188</v>
       </c>
       <c r="H950" s="4">
-        <v>95</v>
+        <v>405</v>
       </c>
       <c r="I950" s="4" t="s">
         <v>189</v>
       </c>
       <c r="J950" s="4">
-        <v>0</v>
+        <v>810</v>
       </c>
       <c r="K950" s="4" t="s">
         <v>25</v>
@@ -39259,34 +39271,34 @@
     </row>
     <row r="951" spans="1:12">
       <c r="A951" s="4" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="B951" s="6">
-        <v>46129</v>
+        <v>46141</v>
       </c>
       <c r="C951" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D951" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="E951" s="4" t="s">
-        <v>196</v>
+        <v>198</v>
+      </c>
+      <c r="E951" s="5" t="s">
+        <v>199</v>
       </c>
       <c r="F951" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G951" s="4" t="s">
-        <v>188</v>
+        <v>28</v>
       </c>
       <c r="H951" s="4">
-        <v>405</v>
+        <v>21</v>
       </c>
       <c r="I951" s="4" t="s">
-        <v>189</v>
+        <v>29</v>
       </c>
       <c r="J951" s="4">
-        <v>810</v>
+        <v>21</v>
       </c>
       <c r="K951" s="4" t="s">
         <v>25</v>
@@ -39308,23 +39320,23 @@
       <c r="D952" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E952" s="5" t="s">
-        <v>199</v>
+      <c r="E952" s="4" t="s">
+        <v>200</v>
       </c>
       <c r="F952" s="4">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G952" s="4" t="s">
-        <v>28</v>
+        <v>119</v>
       </c>
       <c r="H952" s="4">
-        <v>21</v>
+        <v>0.24</v>
       </c>
       <c r="I952" s="4" t="s">
-        <v>29</v>
+        <v>120</v>
       </c>
       <c r="J952" s="4">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K952" s="4" t="s">
         <v>25</v>
@@ -39347,29 +39359,27 @@
         <v>198</v>
       </c>
       <c r="E953" s="4" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F953" s="4">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="G953" s="4" t="s">
-        <v>119</v>
+        <v>28</v>
       </c>
       <c r="H953" s="4">
-        <v>0.24</v>
+        <v>0.95</v>
       </c>
       <c r="I953" s="4" t="s">
-        <v>120</v>
+        <v>29</v>
       </c>
       <c r="J953" s="4">
-        <v>24</v>
+        <v>14.25</v>
       </c>
       <c r="K953" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="L953" s="4" t="s">
-        <v>20</v>
-      </c>
+      <c r="L953" s="4" t="s"/>
     </row>
     <row r="954" spans="1:12">
       <c r="A954" s="4" t="s">
@@ -39384,28 +39394,30 @@
       <c r="D954" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E954" s="4" t="s">
-        <v>201</v>
+      <c r="E954" s="5" t="s">
+        <v>202</v>
       </c>
       <c r="F954" s="4">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="G954" s="4" t="s">
-        <v>28</v>
+        <v>203</v>
       </c>
       <c r="H954" s="4">
-        <v>0.95</v>
+        <v>25</v>
       </c>
       <c r="I954" s="4" t="s">
-        <v>29</v>
+        <v>204</v>
       </c>
       <c r="J954" s="4">
-        <v>14.25</v>
+        <v>50</v>
       </c>
       <c r="K954" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="L954" s="4" t="s"/>
+      <c r="L954" s="4" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="955" spans="1:12">
       <c r="A955" s="4" t="s">
@@ -39420,23 +39432,23 @@
       <c r="D955" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E955" s="5" t="s">
-        <v>202</v>
+      <c r="E955" s="4" t="s">
+        <v>205</v>
       </c>
       <c r="F955" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G955" s="4" t="s">
-        <v>203</v>
+        <v>28</v>
       </c>
       <c r="H955" s="4">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I955" s="4" t="s">
-        <v>204</v>
+        <v>29</v>
       </c>
       <c r="J955" s="4">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="K955" s="4" t="s">
         <v>25</v>
@@ -39458,23 +39470,23 @@
       <c r="D956" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E956" s="4" t="s">
-        <v>205</v>
+      <c r="E956" s="5" t="s">
+        <v>206</v>
       </c>
       <c r="F956" s="4">
         <v>1</v>
       </c>
       <c r="G956" s="4" t="s">
-        <v>28</v>
+        <v>188</v>
       </c>
       <c r="H956" s="4">
-        <v>15</v>
+        <v>370</v>
       </c>
       <c r="I956" s="4" t="s">
-        <v>29</v>
+        <v>189</v>
       </c>
       <c r="J956" s="4">
-        <v>15</v>
+        <v>370</v>
       </c>
       <c r="K956" s="4" t="s">
         <v>25</v>
@@ -39497,22 +39509,22 @@
         <v>198</v>
       </c>
       <c r="E957" s="5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F957" s="4">
-        <v>1</v>
-      </c>
-      <c r="G957" s="4" t="s">
-        <v>188</v>
+        <v>8</v>
+      </c>
+      <c r="G957" s="60" t="s">
+        <v>381</v>
       </c>
       <c r="H957" s="4">
-        <v>370</v>
+        <v>2.8</v>
       </c>
       <c r="I957" s="4" t="s">
-        <v>189</v>
+        <v>120</v>
       </c>
       <c r="J957" s="4">
-        <v>370</v>
+        <v>22.4</v>
       </c>
       <c r="K957" s="4" t="s">
         <v>25</v>
@@ -39534,23 +39546,23 @@
       <c r="D958" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E958" s="5" t="s">
-        <v>207</v>
+      <c r="E958" s="4" t="s">
+        <v>208</v>
       </c>
       <c r="F958" s="4">
-        <v>8</v>
-      </c>
-      <c r="G958" s="60" t="s">
-        <v>381</v>
+        <v>6</v>
+      </c>
+      <c r="G958" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="H958" s="4">
-        <v>2.8</v>
+        <v>11.3</v>
       </c>
       <c r="I958" s="4" t="s">
-        <v>120</v>
+        <v>29</v>
       </c>
       <c r="J958" s="4">
-        <v>22.4</v>
+        <v>67.8</v>
       </c>
       <c r="K958" s="4" t="s">
         <v>25</v>
@@ -39573,22 +39585,22 @@
         <v>198</v>
       </c>
       <c r="E959" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F959" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G959" s="4" t="s">
-        <v>28</v>
+        <v>210</v>
       </c>
       <c r="H959" s="4">
-        <v>11.3</v>
+        <v>45</v>
       </c>
       <c r="I959" s="4" t="s">
-        <v>29</v>
+        <v>211</v>
       </c>
       <c r="J959" s="4">
-        <v>67.8</v>
+        <v>90</v>
       </c>
       <c r="K959" s="4" t="s">
         <v>25</v>
@@ -39610,23 +39622,23 @@
       <c r="D960" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E960" s="4" t="s">
-        <v>209</v>
+      <c r="E960" s="5" t="s">
+        <v>212</v>
       </c>
       <c r="F960" s="4">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G960" s="4" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="H960" s="4">
-        <v>45</v>
+        <v>7.7</v>
       </c>
       <c r="I960" s="4" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="J960" s="4">
-        <v>90</v>
+        <v>115.5</v>
       </c>
       <c r="K960" s="4" t="s">
         <v>25</v>
@@ -39649,22 +39661,22 @@
         <v>198</v>
       </c>
       <c r="E961" s="5" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F961" s="4">
+        <v>5</v>
+      </c>
+      <c r="G961" s="60" t="s">
+        <v>39</v>
+      </c>
+      <c r="H961" s="4">
+        <v>3</v>
+      </c>
+      <c r="I961" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="J961" s="4">
         <v>15</v>
-      </c>
-      <c r="G961" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="H961" s="4">
-        <v>7.7</v>
-      </c>
-      <c r="I961" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="J961" s="4">
-        <v>115.5</v>
       </c>
       <c r="K961" s="4" t="s">
         <v>25</v>
@@ -39687,22 +39699,22 @@
         <v>198</v>
       </c>
       <c r="E962" s="5" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F962" s="4">
-        <v>5</v>
-      </c>
-      <c r="G962" s="60" t="s">
-        <v>39</v>
+        <v>500</v>
+      </c>
+      <c r="G962" s="4" t="s">
+        <v>119</v>
       </c>
       <c r="H962" s="4">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="I962" s="4" t="s">
-        <v>217</v>
+        <v>120</v>
       </c>
       <c r="J962" s="4">
-        <v>15</v>
+        <v>450</v>
       </c>
       <c r="K962" s="4" t="s">
         <v>25</v>
@@ -39724,23 +39736,23 @@
       <c r="D963" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E963" s="5" t="s">
-        <v>218</v>
+      <c r="E963" s="60" t="s">
+        <v>589</v>
       </c>
       <c r="F963" s="4">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="G963" s="4" t="s">
-        <v>119</v>
+        <v>188</v>
       </c>
       <c r="H963" s="4">
-        <v>0.9</v>
+        <v>228</v>
       </c>
       <c r="I963" s="4" t="s">
-        <v>120</v>
+        <v>189</v>
       </c>
       <c r="J963" s="4">
-        <v>450</v>
+        <v>228</v>
       </c>
       <c r="K963" s="4" t="s">
         <v>25</v>
@@ -39762,8 +39774,8 @@
       <c r="D964" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E964" s="5" t="s">
-        <v>219</v>
+      <c r="E964" s="60" t="s">
+        <v>590</v>
       </c>
       <c r="F964" s="4">
         <v>1</v>
@@ -39772,13 +39784,13 @@
         <v>188</v>
       </c>
       <c r="H964" s="4">
-        <v>228</v>
+        <v>282</v>
       </c>
       <c r="I964" s="4" t="s">
         <v>189</v>
       </c>
       <c r="J964" s="4">
-        <v>228</v>
+        <v>282</v>
       </c>
       <c r="K964" s="4" t="s">
         <v>25</v>
@@ -39801,22 +39813,22 @@
         <v>198</v>
       </c>
       <c r="E965" s="5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F965" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G965" s="4" t="s">
         <v>188</v>
       </c>
       <c r="H965" s="4">
-        <v>282</v>
+        <v>132</v>
       </c>
       <c r="I965" s="4" t="s">
         <v>189</v>
       </c>
       <c r="J965" s="4">
-        <v>282</v>
+        <v>264</v>
       </c>
       <c r="K965" s="4" t="s">
         <v>25</v>
@@ -39838,23 +39850,23 @@
       <c r="D966" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E966" s="5" t="s">
-        <v>221</v>
+      <c r="E966" s="60" t="s">
+        <v>584</v>
       </c>
       <c r="F966" s="4">
         <v>2</v>
       </c>
       <c r="G966" s="4" t="s">
-        <v>188</v>
+        <v>44</v>
       </c>
       <c r="H966" s="4">
-        <v>132</v>
+        <v>32</v>
       </c>
       <c r="I966" s="4" t="s">
-        <v>189</v>
+        <v>45</v>
       </c>
       <c r="J966" s="4">
-        <v>264</v>
+        <v>64</v>
       </c>
       <c r="K966" s="4" t="s">
         <v>25</v>
@@ -39868,7 +39880,7 @@
         <v>197</v>
       </c>
       <c r="B967" s="6">
-        <v>46141</v>
+        <v>46113</v>
       </c>
       <c r="C967" s="4" t="s">
         <v>14</v>
@@ -39876,23 +39888,23 @@
       <c r="D967" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E967" s="60" t="s">
-        <v>584</v>
+      <c r="E967" s="5" t="s">
+        <v>223</v>
       </c>
       <c r="F967" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G967" s="4" t="s">
-        <v>44</v>
+        <v>213</v>
       </c>
       <c r="H967" s="4">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I967" s="4" t="s">
-        <v>45</v>
+        <v>214</v>
       </c>
       <c r="J967" s="4">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="K967" s="4" t="s">
         <v>25</v>
@@ -39906,7 +39918,7 @@
         <v>197</v>
       </c>
       <c r="B968" s="6">
-        <v>46113</v>
+        <v>46128</v>
       </c>
       <c r="C968" s="4" t="s">
         <v>14</v>
@@ -39914,23 +39926,23 @@
       <c r="D968" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E968" s="5" t="s">
-        <v>223</v>
+      <c r="E968" s="4" t="s">
+        <v>208</v>
       </c>
       <c r="F968" s="4">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G968" s="4" t="s">
-        <v>213</v>
+        <v>28</v>
       </c>
       <c r="H968" s="4">
-        <v>37</v>
+        <v>11.3</v>
       </c>
       <c r="I968" s="4" t="s">
-        <v>214</v>
+        <v>29</v>
       </c>
       <c r="J968" s="4">
-        <v>37</v>
+        <v>135.6</v>
       </c>
       <c r="K968" s="4" t="s">
         <v>25</v>
@@ -39953,22 +39965,22 @@
         <v>198</v>
       </c>
       <c r="E969" s="4" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="F969" s="4">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G969" s="4" t="s">
         <v>28</v>
       </c>
       <c r="H969" s="4">
-        <v>11.3</v>
+        <v>18</v>
       </c>
       <c r="I969" s="4" t="s">
         <v>29</v>
       </c>
       <c r="J969" s="4">
-        <v>135.6</v>
+        <v>18</v>
       </c>
       <c r="K969" s="4" t="s">
         <v>25</v>
@@ -39991,7 +40003,7 @@
         <v>198</v>
       </c>
       <c r="E970" s="4" t="s">
-        <v>224</v>
+        <v>205</v>
       </c>
       <c r="F970" s="4">
         <v>1</v>
@@ -40000,13 +40012,13 @@
         <v>28</v>
       </c>
       <c r="H970" s="4">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I970" s="4" t="s">
         <v>29</v>
       </c>
       <c r="J970" s="4">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="K970" s="4" t="s">
         <v>25</v>
@@ -40029,22 +40041,22 @@
         <v>198</v>
       </c>
       <c r="E971" s="4" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="F971" s="4">
         <v>1</v>
       </c>
       <c r="G971" s="4" t="s">
-        <v>28</v>
+        <v>210</v>
       </c>
       <c r="H971" s="4">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="I971" s="4" t="s">
-        <v>29</v>
+        <v>211</v>
       </c>
       <c r="J971" s="4">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="K971" s="4" t="s">
         <v>25</v>
@@ -40066,23 +40078,23 @@
       <c r="D972" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E972" s="4" t="s">
-        <v>209</v>
+      <c r="E972" s="5" t="s">
+        <v>212</v>
       </c>
       <c r="F972" s="4">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="G972" s="4" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="H972" s="4">
-        <v>45</v>
+        <v>7.7</v>
       </c>
       <c r="I972" s="4" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="J972" s="4">
-        <v>45</v>
+        <v>154</v>
       </c>
       <c r="K972" s="4" t="s">
         <v>25</v>
@@ -40105,22 +40117,22 @@
         <v>198</v>
       </c>
       <c r="E973" s="5" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="F973" s="4">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="G973" s="4" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="H973" s="4">
-        <v>7.7</v>
+        <v>25</v>
       </c>
       <c r="I973" s="4" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="J973" s="4">
-        <v>154</v>
+        <v>50</v>
       </c>
       <c r="K973" s="4" t="s">
         <v>25</v>
@@ -40142,23 +40154,23 @@
       <c r="D974" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E974" s="5" t="s">
-        <v>202</v>
+      <c r="E974" s="4" t="s">
+        <v>225</v>
       </c>
       <c r="F974" s="4">
         <v>2</v>
       </c>
       <c r="G974" s="4" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="H974" s="4">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="I974" s="4" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="J974" s="4">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="K974" s="4" t="s">
         <v>25</v>
@@ -40180,23 +40192,23 @@
       <c r="D975" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E975" s="4" t="s">
-        <v>225</v>
+      <c r="E975" s="5" t="s">
+        <v>199</v>
       </c>
       <c r="F975" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G975" s="4" t="s">
-        <v>226</v>
+        <v>28</v>
       </c>
       <c r="H975" s="4">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="I975" s="4" t="s">
-        <v>227</v>
+        <v>29</v>
       </c>
       <c r="J975" s="4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K975" s="4" t="s">
         <v>25</v>
@@ -40218,23 +40230,23 @@
       <c r="D976" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E976" s="5" t="s">
-        <v>199</v>
+      <c r="E976" s="60" t="s">
+        <v>590</v>
       </c>
       <c r="F976" s="4">
         <v>1</v>
       </c>
       <c r="G976" s="4" t="s">
-        <v>28</v>
+        <v>188</v>
       </c>
       <c r="H976" s="4">
-        <v>21</v>
+        <v>282</v>
       </c>
       <c r="I976" s="4" t="s">
-        <v>29</v>
+        <v>189</v>
       </c>
       <c r="J976" s="4">
-        <v>21</v>
+        <v>282</v>
       </c>
       <c r="K976" s="4" t="s">
         <v>25</v>
@@ -40256,8 +40268,8 @@
       <c r="D977" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E977" s="5" t="s">
-        <v>220</v>
+      <c r="E977" s="60" t="s">
+        <v>589</v>
       </c>
       <c r="F977" s="4">
         <v>1</v>
@@ -40266,13 +40278,13 @@
         <v>188</v>
       </c>
       <c r="H977" s="4">
-        <v>282</v>
+        <v>228</v>
       </c>
       <c r="I977" s="4" t="s">
         <v>189</v>
       </c>
       <c r="J977" s="4">
-        <v>282</v>
+        <v>228</v>
       </c>
       <c r="K977" s="4" t="s">
         <v>25</v>
@@ -40295,22 +40307,22 @@
         <v>198</v>
       </c>
       <c r="E978" s="5" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F978" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G978" s="4" t="s">
         <v>188</v>
       </c>
       <c r="H978" s="4">
-        <v>228</v>
+        <v>132</v>
       </c>
       <c r="I978" s="4" t="s">
         <v>189</v>
       </c>
       <c r="J978" s="4">
-        <v>228</v>
+        <v>264</v>
       </c>
       <c r="K978" s="4" t="s">
         <v>25</v>
@@ -40332,23 +40344,23 @@
       <c r="D979" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E979" s="5" t="s">
-        <v>221</v>
+      <c r="E979" s="4" t="s">
+        <v>228</v>
       </c>
       <c r="F979" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G979" s="4" t="s">
-        <v>188</v>
+        <v>44</v>
       </c>
       <c r="H979" s="4">
-        <v>132</v>
+        <v>580</v>
       </c>
       <c r="I979" s="4" t="s">
-        <v>189</v>
+        <v>45</v>
       </c>
       <c r="J979" s="4">
-        <v>264</v>
+        <v>580</v>
       </c>
       <c r="K979" s="4" t="s">
         <v>25</v>
@@ -40371,22 +40383,22 @@
         <v>198</v>
       </c>
       <c r="E980" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F980" s="4">
         <v>1</v>
       </c>
       <c r="G980" s="4" t="s">
-        <v>44</v>
+        <v>188</v>
       </c>
       <c r="H980" s="4">
-        <v>580</v>
+        <v>180</v>
       </c>
       <c r="I980" s="4" t="s">
-        <v>45</v>
+        <v>189</v>
       </c>
       <c r="J980" s="4">
-        <v>580</v>
+        <v>180</v>
       </c>
       <c r="K980" s="4" t="s">
         <v>25</v>
@@ -40408,23 +40420,23 @@
       <c r="D981" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E981" s="4" t="s">
-        <v>229</v>
+      <c r="E981" s="5" t="s">
+        <v>230</v>
       </c>
       <c r="F981" s="4">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="G981" s="4" t="s">
-        <v>188</v>
+        <v>119</v>
       </c>
       <c r="H981" s="4">
-        <v>180</v>
+        <v>1.2</v>
       </c>
       <c r="I981" s="4" t="s">
-        <v>189</v>
+        <v>120</v>
       </c>
       <c r="J981" s="4">
-        <v>180</v>
+        <v>600</v>
       </c>
       <c r="K981" s="4" t="s">
         <v>25</v>
@@ -40447,22 +40459,22 @@
         <v>198</v>
       </c>
       <c r="E982" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F982" s="4">
-        <v>500</v>
-      </c>
-      <c r="G982" s="4" t="s">
-        <v>119</v>
+        <v>1</v>
+      </c>
+      <c r="G982" s="60" t="s">
+        <v>28</v>
       </c>
       <c r="H982" s="4">
-        <v>1.2</v>
-      </c>
-      <c r="I982" s="4" t="s">
-        <v>120</v>
+        <v>65</v>
+      </c>
+      <c r="I982" s="60" t="s">
+        <v>45</v>
       </c>
       <c r="J982" s="4">
-        <v>600</v>
+        <v>65</v>
       </c>
       <c r="K982" s="4" t="s">
         <v>25</v>
@@ -40476,7 +40488,7 @@
         <v>197</v>
       </c>
       <c r="B983" s="6">
-        <v>46128</v>
+        <v>46113</v>
       </c>
       <c r="C983" s="4" t="s">
         <v>14</v>
@@ -40485,22 +40497,22 @@
         <v>198</v>
       </c>
       <c r="E983" s="5" t="s">
-        <v>231</v>
+        <v>212</v>
       </c>
       <c r="F983" s="4">
-        <v>1</v>
-      </c>
-      <c r="G983" s="60" t="s">
-        <v>44</v>
+        <v>4</v>
+      </c>
+      <c r="G983" s="4" t="s">
+        <v>213</v>
       </c>
       <c r="H983" s="4">
-        <v>65</v>
-      </c>
-      <c r="I983" s="60" t="s">
-        <v>45</v>
+        <v>9.5</v>
+      </c>
+      <c r="I983" s="4" t="s">
+        <v>214</v>
       </c>
       <c r="J983" s="4">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="K983" s="4" t="s">
         <v>25</v>
@@ -40522,23 +40534,23 @@
       <c r="D984" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E984" s="5" t="s">
-        <v>212</v>
+      <c r="E984" s="4" t="s">
+        <v>200</v>
       </c>
       <c r="F984" s="4">
-        <v>4</v>
+        <v>100</v>
       </c>
       <c r="G984" s="4" t="s">
-        <v>213</v>
+        <v>119</v>
       </c>
       <c r="H984" s="4">
-        <v>9.5</v>
+        <v>0.24</v>
       </c>
       <c r="I984" s="4" t="s">
-        <v>214</v>
+        <v>120</v>
       </c>
       <c r="J984" s="4">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="K984" s="4" t="s">
         <v>25</v>
@@ -40552,7 +40564,7 @@
         <v>197</v>
       </c>
       <c r="B985" s="6">
-        <v>46113</v>
+        <v>46126</v>
       </c>
       <c r="C985" s="4" t="s">
         <v>14</v>
@@ -40561,22 +40573,22 @@
         <v>198</v>
       </c>
       <c r="E985" s="4" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="F985" s="4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G985" s="4" t="s">
-        <v>119</v>
+        <v>28</v>
       </c>
       <c r="H985" s="4">
-        <v>0.24</v>
+        <v>11.3</v>
       </c>
       <c r="I985" s="4" t="s">
-        <v>120</v>
+        <v>29</v>
       </c>
       <c r="J985" s="4">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K985" s="4" t="s">
         <v>25</v>
@@ -40598,20 +40610,20 @@
       <c r="D986" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E986" s="4" t="s">
-        <v>208</v>
+      <c r="E986" s="60" t="s">
+        <v>589</v>
       </c>
       <c r="F986" s="4">
         <v>0</v>
       </c>
       <c r="G986" s="4" t="s">
-        <v>28</v>
+        <v>188</v>
       </c>
       <c r="H986" s="4">
-        <v>11.3</v>
+        <v>228</v>
       </c>
       <c r="I986" s="4" t="s">
-        <v>29</v>
+        <v>189</v>
       </c>
       <c r="J986" s="4">
         <v>0</v>
@@ -40628,7 +40640,7 @@
         <v>197</v>
       </c>
       <c r="B987" s="6">
-        <v>46126</v>
+        <v>46135</v>
       </c>
       <c r="C987" s="4" t="s">
         <v>14</v>
@@ -40636,23 +40648,23 @@
       <c r="D987" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E987" s="5" t="s">
-        <v>219</v>
+      <c r="E987" s="4" t="s">
+        <v>208</v>
       </c>
       <c r="F987" s="4">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G987" s="4" t="s">
-        <v>188</v>
+        <v>28</v>
       </c>
       <c r="H987" s="4">
-        <v>228</v>
+        <v>11.3</v>
       </c>
       <c r="I987" s="4" t="s">
-        <v>189</v>
+        <v>29</v>
       </c>
       <c r="J987" s="4">
-        <v>0</v>
+        <v>158.2</v>
       </c>
       <c r="K987" s="4" t="s">
         <v>25</v>
@@ -40674,23 +40686,23 @@
       <c r="D988" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E988" s="4" t="s">
-        <v>208</v>
+      <c r="E988" s="5" t="s">
+        <v>212</v>
       </c>
       <c r="F988" s="4">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="G988" s="4" t="s">
-        <v>28</v>
+        <v>213</v>
       </c>
       <c r="H988" s="4">
-        <v>11.3</v>
+        <v>9.5</v>
       </c>
       <c r="I988" s="4" t="s">
-        <v>29</v>
+        <v>214</v>
       </c>
       <c r="J988" s="4">
-        <v>158.2</v>
+        <v>28.5</v>
       </c>
       <c r="K988" s="4" t="s">
         <v>25</v>
@@ -40713,22 +40725,22 @@
         <v>198</v>
       </c>
       <c r="E989" s="5" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="F989" s="4">
-        <v>3</v>
-      </c>
-      <c r="G989" s="4" t="s">
-        <v>213</v>
+        <v>5</v>
+      </c>
+      <c r="G989" s="60" t="s">
+        <v>376</v>
       </c>
       <c r="H989" s="4">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="I989" s="4" t="s">
-        <v>214</v>
+        <v>29</v>
       </c>
       <c r="J989" s="4">
-        <v>28.5</v>
+        <v>50</v>
       </c>
       <c r="K989" s="4" t="s">
         <v>25</v>
@@ -40751,19 +40763,19 @@
         <v>198</v>
       </c>
       <c r="E990" s="5" t="s">
-        <v>232</v>
+        <v>202</v>
       </c>
       <c r="F990" s="4">
-        <v>5</v>
-      </c>
-      <c r="G990" s="60" t="s">
-        <v>376</v>
+        <v>2</v>
+      </c>
+      <c r="G990" s="4" t="s">
+        <v>203</v>
       </c>
       <c r="H990" s="4">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="I990" s="4" t="s">
-        <v>29</v>
+        <v>204</v>
       </c>
       <c r="J990" s="4">
         <v>50</v>
@@ -40789,22 +40801,22 @@
         <v>198</v>
       </c>
       <c r="E991" s="5" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F991" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G991" s="4" t="s">
-        <v>203</v>
+        <v>28</v>
       </c>
       <c r="H991" s="4">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="I991" s="4" t="s">
-        <v>204</v>
+        <v>29</v>
       </c>
       <c r="J991" s="4">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="K991" s="4" t="s">
         <v>25</v>
@@ -40826,8 +40838,8 @@
       <c r="D992" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E992" s="5" t="s">
-        <v>199</v>
+      <c r="E992" s="4" t="s">
+        <v>205</v>
       </c>
       <c r="F992" s="4">
         <v>1</v>
@@ -40836,13 +40848,13 @@
         <v>28</v>
       </c>
       <c r="H992" s="4">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I992" s="4" t="s">
         <v>29</v>
       </c>
       <c r="J992" s="4">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="K992" s="4" t="s">
         <v>25</v>
@@ -40865,22 +40877,22 @@
         <v>198</v>
       </c>
       <c r="E993" s="4" t="s">
-        <v>205</v>
+        <v>233</v>
       </c>
       <c r="F993" s="4">
         <v>1</v>
       </c>
       <c r="G993" s="4" t="s">
-        <v>28</v>
+        <v>188</v>
       </c>
       <c r="H993" s="4">
-        <v>15</v>
+        <v>114</v>
       </c>
       <c r="I993" s="4" t="s">
-        <v>29</v>
+        <v>189</v>
       </c>
       <c r="J993" s="4">
-        <v>15</v>
+        <v>114</v>
       </c>
       <c r="K993" s="4" t="s">
         <v>25</v>
@@ -40902,8 +40914,8 @@
       <c r="D994" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E994" s="4" t="s">
-        <v>233</v>
+      <c r="E994" s="5" t="s">
+        <v>234</v>
       </c>
       <c r="F994" s="4">
         <v>1</v>
@@ -40912,13 +40924,13 @@
         <v>188</v>
       </c>
       <c r="H994" s="4">
-        <v>114</v>
+        <v>155</v>
       </c>
       <c r="I994" s="4" t="s">
         <v>189</v>
       </c>
       <c r="J994" s="4">
-        <v>114</v>
+        <v>155</v>
       </c>
       <c r="K994" s="4" t="s">
         <v>25</v>
@@ -40941,22 +40953,22 @@
         <v>198</v>
       </c>
       <c r="E995" s="5" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F995" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G995" s="4" t="s">
-        <v>188</v>
+        <v>213</v>
       </c>
       <c r="H995" s="4">
-        <v>155</v>
+        <v>32</v>
       </c>
       <c r="I995" s="4" t="s">
-        <v>189</v>
+        <v>214</v>
       </c>
       <c r="J995" s="4">
-        <v>155</v>
+        <v>64</v>
       </c>
       <c r="K995" s="4" t="s">
         <v>25</v>
@@ -40979,22 +40991,22 @@
         <v>198</v>
       </c>
       <c r="E996" s="5" t="s">
-        <v>235</v>
+        <v>221</v>
       </c>
       <c r="F996" s="4">
         <v>2</v>
       </c>
       <c r="G996" s="4" t="s">
-        <v>213</v>
+        <v>188</v>
       </c>
       <c r="H996" s="4">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="I996" s="4" t="s">
-        <v>214</v>
+        <v>189</v>
       </c>
       <c r="J996" s="4">
-        <v>64</v>
+        <v>264</v>
       </c>
       <c r="K996" s="4" t="s">
         <v>25</v>
@@ -41016,23 +41028,23 @@
       <c r="D997" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E997" s="5" t="s">
-        <v>221</v>
+      <c r="E997" s="60" t="s">
+        <v>590</v>
       </c>
       <c r="F997" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G997" s="4" t="s">
         <v>188</v>
       </c>
       <c r="H997" s="4">
-        <v>132</v>
+        <v>282</v>
       </c>
       <c r="I997" s="4" t="s">
         <v>189</v>
       </c>
       <c r="J997" s="4">
-        <v>264</v>
+        <v>282</v>
       </c>
       <c r="K997" s="4" t="s">
         <v>25</v>
@@ -41054,8 +41066,8 @@
       <c r="D998" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E998" s="5" t="s">
-        <v>220</v>
+      <c r="E998" s="60" t="s">
+        <v>589</v>
       </c>
       <c r="F998" s="4">
         <v>1</v>
@@ -41064,13 +41076,13 @@
         <v>188</v>
       </c>
       <c r="H998" s="4">
-        <v>282</v>
+        <v>228</v>
       </c>
       <c r="I998" s="4" t="s">
         <v>189</v>
       </c>
       <c r="J998" s="4">
-        <v>282</v>
+        <v>228</v>
       </c>
       <c r="K998" s="4" t="s">
         <v>25</v>
@@ -41092,23 +41104,23 @@
       <c r="D999" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E999" s="5" t="s">
-        <v>219</v>
+      <c r="E999" s="60" t="s">
+        <v>584</v>
       </c>
       <c r="F999" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G999" s="4" t="s">
-        <v>188</v>
+        <v>44</v>
       </c>
       <c r="H999" s="4">
-        <v>228</v>
+        <v>32</v>
       </c>
       <c r="I999" s="4" t="s">
-        <v>189</v>
+        <v>45</v>
       </c>
       <c r="J999" s="4">
-        <v>228</v>
+        <v>64</v>
       </c>
       <c r="K999" s="4" t="s">
         <v>25</v>
@@ -41130,23 +41142,23 @@
       <c r="D1000" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E1000" s="60" t="s">
-        <v>584</v>
+      <c r="E1000" s="5" t="s">
+        <v>230</v>
       </c>
       <c r="F1000" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1000" s="4" t="s">
-        <v>44</v>
+        <v>119</v>
       </c>
       <c r="H1000" s="4">
-        <v>32</v>
+        <v>1.2</v>
       </c>
       <c r="I1000" s="4" t="s">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="J1000" s="4">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="K1000" s="4" t="s">
         <v>25</v>
@@ -41169,22 +41181,22 @@
         <v>198</v>
       </c>
       <c r="E1001" s="5" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="F1001" s="4">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G1001" s="4" t="s">
         <v>119</v>
       </c>
       <c r="H1001" s="4">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="I1001" s="4" t="s">
         <v>120</v>
       </c>
       <c r="J1001" s="4">
-        <v>0</v>
+        <v>450</v>
       </c>
       <c r="K1001" s="4" t="s">
         <v>25</v>
@@ -41207,22 +41219,22 @@
         <v>198</v>
       </c>
       <c r="E1002" s="5" t="s">
-        <v>218</v>
+        <v>237</v>
       </c>
       <c r="F1002" s="4">
-        <v>500</v>
+        <v>10</v>
       </c>
       <c r="G1002" s="4" t="s">
-        <v>119</v>
+        <v>44</v>
       </c>
       <c r="H1002" s="4">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="I1002" s="4" t="s">
-        <v>120</v>
+        <v>45</v>
       </c>
       <c r="J1002" s="4">
-        <v>450</v>
+        <v>15</v>
       </c>
       <c r="K1002" s="4" t="s">
         <v>25</v>
@@ -41236,7 +41248,7 @@
         <v>197</v>
       </c>
       <c r="B1003" s="6">
-        <v>46135</v>
+        <v>46123</v>
       </c>
       <c r="C1003" s="4" t="s">
         <v>14</v>
@@ -41245,22 +41257,22 @@
         <v>198</v>
       </c>
       <c r="E1003" s="5" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F1003" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G1003" s="4" t="s">
-        <v>44</v>
+        <v>188</v>
       </c>
       <c r="H1003" s="4">
-        <v>1.5</v>
+        <v>285</v>
       </c>
       <c r="I1003" s="4" t="s">
-        <v>45</v>
+        <v>189</v>
       </c>
       <c r="J1003" s="4">
-        <v>15</v>
+        <v>285</v>
       </c>
       <c r="K1003" s="4" t="s">
         <v>25</v>
@@ -41283,22 +41295,22 @@
         <v>198</v>
       </c>
       <c r="E1004" s="5" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F1004" s="4">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="G1004" s="4" t="s">
-        <v>188</v>
+        <v>119</v>
       </c>
       <c r="H1004" s="4">
-        <v>285</v>
+        <v>0.15</v>
       </c>
       <c r="I1004" s="4" t="s">
-        <v>189</v>
+        <v>120</v>
       </c>
       <c r="J1004" s="4">
-        <v>285</v>
+        <v>150</v>
       </c>
       <c r="K1004" s="4" t="s">
         <v>25</v>
@@ -41321,22 +41333,22 @@
         <v>198</v>
       </c>
       <c r="E1005" s="5" t="s">
-        <v>239</v>
+        <v>202</v>
       </c>
       <c r="F1005" s="4">
-        <v>1000</v>
+        <v>2</v>
       </c>
       <c r="G1005" s="4" t="s">
-        <v>119</v>
+        <v>203</v>
       </c>
       <c r="H1005" s="4">
-        <v>0.15</v>
+        <v>25</v>
       </c>
       <c r="I1005" s="4" t="s">
-        <v>120</v>
+        <v>204</v>
       </c>
       <c r="J1005" s="4">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="K1005" s="4" t="s">
         <v>25</v>
@@ -41359,22 +41371,22 @@
         <v>198</v>
       </c>
       <c r="E1006" s="5" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="F1006" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1006" s="4" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="H1006" s="4">
-        <v>25</v>
+        <v>370</v>
       </c>
       <c r="I1006" s="4" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="J1006" s="4">
-        <v>50</v>
+        <v>370</v>
       </c>
       <c r="K1006" s="4" t="s">
         <v>25</v>
@@ -41396,23 +41408,23 @@
       <c r="D1007" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E1007" s="5" t="s">
-        <v>206</v>
+      <c r="E1007" s="4" t="s">
+        <v>208</v>
       </c>
       <c r="F1007" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G1007" s="4" t="s">
-        <v>188</v>
+        <v>28</v>
       </c>
       <c r="H1007" s="4">
-        <v>370</v>
+        <v>11.3</v>
       </c>
       <c r="I1007" s="4" t="s">
-        <v>189</v>
+        <v>29</v>
       </c>
       <c r="J1007" s="4">
-        <v>370</v>
+        <v>67.8</v>
       </c>
       <c r="K1007" s="4" t="s">
         <v>25</v>
@@ -41434,23 +41446,23 @@
       <c r="D1008" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E1008" s="4" t="s">
-        <v>208</v>
+      <c r="E1008" s="5" t="s">
+        <v>212</v>
       </c>
       <c r="F1008" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1008" s="4" t="s">
-        <v>28</v>
+        <v>213</v>
       </c>
       <c r="H1008" s="4">
-        <v>11.3</v>
+        <v>7.7</v>
       </c>
       <c r="I1008" s="4" t="s">
-        <v>29</v>
+        <v>214</v>
       </c>
       <c r="J1008" s="4">
-        <v>67.8</v>
+        <v>30.8</v>
       </c>
       <c r="K1008" s="4" t="s">
         <v>25</v>
@@ -41473,22 +41485,22 @@
         <v>198</v>
       </c>
       <c r="E1009" s="5" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="F1009" s="4">
-        <v>4</v>
-      </c>
-      <c r="G1009" s="4" t="s">
-        <v>213</v>
+        <v>3</v>
+      </c>
+      <c r="G1009" s="60" t="s">
+        <v>376</v>
       </c>
       <c r="H1009" s="4">
-        <v>7.7</v>
+        <v>10</v>
       </c>
       <c r="I1009" s="4" t="s">
-        <v>214</v>
+        <v>29</v>
       </c>
       <c r="J1009" s="4">
-        <v>30.8</v>
+        <v>30</v>
       </c>
       <c r="K1009" s="4" t="s">
         <v>25</v>
@@ -41510,23 +41522,23 @@
       <c r="D1010" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E1010" s="5" t="s">
-        <v>232</v>
+      <c r="E1010" s="4" t="s">
+        <v>209</v>
       </c>
       <c r="F1010" s="4">
-        <v>3</v>
-      </c>
-      <c r="G1010" s="60" t="s">
-        <v>376</v>
+        <v>1</v>
+      </c>
+      <c r="G1010" s="4" t="s">
+        <v>210</v>
       </c>
       <c r="H1010" s="4">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="I1010" s="4" t="s">
-        <v>29</v>
+        <v>211</v>
       </c>
       <c r="J1010" s="4">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="K1010" s="4" t="s">
         <v>25</v>
@@ -41549,22 +41561,22 @@
         <v>198</v>
       </c>
       <c r="E1011" s="4" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="F1011" s="4">
         <v>1</v>
       </c>
       <c r="G1011" s="4" t="s">
-        <v>210</v>
+        <v>28</v>
       </c>
       <c r="H1011" s="4">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="I1011" s="4" t="s">
-        <v>211</v>
+        <v>29</v>
       </c>
       <c r="J1011" s="4">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="K1011" s="4" t="s">
         <v>25</v>
@@ -41586,23 +41598,23 @@
       <c r="D1012" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E1012" s="4" t="s">
-        <v>205</v>
+      <c r="E1012" s="5" t="s">
+        <v>221</v>
       </c>
       <c r="F1012" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1012" s="4" t="s">
-        <v>28</v>
+        <v>188</v>
       </c>
       <c r="H1012" s="4">
-        <v>15</v>
+        <v>132</v>
       </c>
       <c r="I1012" s="4" t="s">
-        <v>29</v>
+        <v>189</v>
       </c>
       <c r="J1012" s="4">
-        <v>15</v>
+        <v>264</v>
       </c>
       <c r="K1012" s="4" t="s">
         <v>25</v>
@@ -41624,23 +41636,23 @@
       <c r="D1013" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E1013" s="5" t="s">
-        <v>221</v>
+      <c r="E1013" s="60" t="s">
+        <v>590</v>
       </c>
       <c r="F1013" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1013" s="4" t="s">
         <v>188</v>
       </c>
       <c r="H1013" s="4">
-        <v>132</v>
+        <v>282</v>
       </c>
       <c r="I1013" s="4" t="s">
         <v>189</v>
       </c>
       <c r="J1013" s="4">
-        <v>264</v>
+        <v>282</v>
       </c>
       <c r="K1013" s="4" t="s">
         <v>25</v>
@@ -41662,23 +41674,23 @@
       <c r="D1014" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E1014" s="5" t="s">
-        <v>220</v>
+      <c r="E1014" s="60" t="s">
+        <v>589</v>
       </c>
       <c r="F1014" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1014" s="4" t="s">
         <v>188</v>
       </c>
       <c r="H1014" s="4">
-        <v>282</v>
+        <v>228</v>
       </c>
       <c r="I1014" s="4" t="s">
         <v>189</v>
       </c>
       <c r="J1014" s="4">
-        <v>282</v>
+        <v>456</v>
       </c>
       <c r="K1014" s="4" t="s">
         <v>25</v>
@@ -41700,8 +41712,8 @@
       <c r="D1015" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E1015" s="5" t="s">
-        <v>219</v>
+      <c r="E1015" s="4" t="s">
+        <v>240</v>
       </c>
       <c r="F1015" s="4">
         <v>2</v>
@@ -41710,13 +41722,13 @@
         <v>188</v>
       </c>
       <c r="H1015" s="4">
-        <v>228</v>
+        <v>114</v>
       </c>
       <c r="I1015" s="4" t="s">
         <v>189</v>
       </c>
       <c r="J1015" s="4">
-        <v>456</v>
+        <v>228</v>
       </c>
       <c r="K1015" s="4" t="s">
         <v>25</v>
@@ -41739,7 +41751,7 @@
         <v>198</v>
       </c>
       <c r="E1016" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F1016" s="4">
         <v>2</v>
@@ -41748,13 +41760,13 @@
         <v>188</v>
       </c>
       <c r="H1016" s="4">
-        <v>114</v>
+        <v>66</v>
       </c>
       <c r="I1016" s="4" t="s">
         <v>189</v>
       </c>
       <c r="J1016" s="4">
-        <v>228</v>
+        <v>132</v>
       </c>
       <c r="K1016" s="4" t="s">
         <v>25</v>
@@ -41776,23 +41788,23 @@
       <c r="D1017" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E1017" s="4" t="s">
-        <v>241</v>
+      <c r="E1017" s="5" t="s">
+        <v>230</v>
       </c>
       <c r="F1017" s="4">
-        <v>2</v>
+        <v>500</v>
       </c>
       <c r="G1017" s="4" t="s">
-        <v>188</v>
+        <v>119</v>
       </c>
       <c r="H1017" s="4">
-        <v>66</v>
+        <v>1.2</v>
       </c>
       <c r="I1017" s="4" t="s">
-        <v>189</v>
+        <v>120</v>
       </c>
       <c r="J1017" s="4">
-        <v>132</v>
+        <v>600</v>
       </c>
       <c r="K1017" s="4" t="s">
         <v>25</v>
@@ -41814,23 +41826,23 @@
       <c r="D1018" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E1018" s="5" t="s">
-        <v>230</v>
+      <c r="E1018" s="4" t="s">
+        <v>242</v>
       </c>
       <c r="F1018" s="4">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="G1018" s="4" t="s">
-        <v>119</v>
+        <v>210</v>
       </c>
       <c r="H1018" s="4">
-        <v>1.2</v>
+        <v>95</v>
       </c>
       <c r="I1018" s="4" t="s">
-        <v>120</v>
+        <v>211</v>
       </c>
       <c r="J1018" s="4">
-        <v>600</v>
+        <v>95</v>
       </c>
       <c r="K1018" s="4" t="s">
         <v>25</v>
@@ -41852,23 +41864,23 @@
       <c r="D1019" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E1019" s="4" t="s">
-        <v>242</v>
+      <c r="E1019" s="5" t="s">
+        <v>243</v>
       </c>
       <c r="F1019" s="4">
         <v>1</v>
       </c>
       <c r="G1019" s="4" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
       <c r="H1019" s="4">
-        <v>95</v>
+        <v>680</v>
       </c>
       <c r="I1019" s="4" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="J1019" s="4">
-        <v>95</v>
+        <v>680</v>
       </c>
       <c r="K1019" s="4" t="s">
         <v>25</v>
@@ -41891,22 +41903,22 @@
         <v>198</v>
       </c>
       <c r="E1020" s="5" t="s">
-        <v>243</v>
+        <v>215</v>
       </c>
       <c r="F1020" s="4">
-        <v>1</v>
-      </c>
-      <c r="G1020" s="4" t="s">
-        <v>188</v>
+        <v>5</v>
+      </c>
+      <c r="G1020" s="60" t="s">
+        <v>39</v>
       </c>
       <c r="H1020" s="4">
-        <v>680</v>
+        <v>3</v>
       </c>
       <c r="I1020" s="4" t="s">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="J1020" s="4">
-        <v>680</v>
+        <v>15</v>
       </c>
       <c r="K1020" s="4" t="s">
         <v>25</v>
@@ -41929,22 +41941,22 @@
         <v>198</v>
       </c>
       <c r="E1021" s="5" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="F1021" s="4">
-        <v>5</v>
-      </c>
-      <c r="G1021" s="60" t="s">
-        <v>39</v>
+        <v>2</v>
+      </c>
+      <c r="G1021" s="4" t="s">
+        <v>213</v>
       </c>
       <c r="H1021" s="4">
-        <v>3</v>
+        <v>32.5</v>
       </c>
       <c r="I1021" s="4" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="J1021" s="4">
-        <v>15</v>
+        <v>65</v>
       </c>
       <c r="K1021" s="4" t="s">
         <v>25</v>
@@ -41958,7 +41970,7 @@
         <v>197</v>
       </c>
       <c r="B1022" s="6">
-        <v>46123</v>
+        <v>46141</v>
       </c>
       <c r="C1022" s="4" t="s">
         <v>14</v>
@@ -41966,23 +41978,23 @@
       <c r="D1022" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E1022" s="5" t="s">
-        <v>235</v>
+      <c r="E1022" s="4" t="s">
+        <v>228</v>
       </c>
       <c r="F1022" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1022" s="4" t="s">
-        <v>213</v>
+        <v>44</v>
       </c>
       <c r="H1022" s="4">
-        <v>32.5</v>
+        <v>630</v>
       </c>
       <c r="I1022" s="4" t="s">
-        <v>214</v>
+        <v>45</v>
       </c>
       <c r="J1022" s="4">
-        <v>65</v>
+        <v>630</v>
       </c>
       <c r="K1022" s="4" t="s">
         <v>25</v>
@@ -42004,23 +42016,23 @@
       <c r="D1023" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E1023" s="4" t="s">
-        <v>228</v>
+      <c r="E1023" s="5" t="s">
+        <v>212</v>
       </c>
       <c r="F1023" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1023" s="4" t="s">
-        <v>44</v>
+        <v>213</v>
       </c>
       <c r="H1023" s="4">
-        <v>630</v>
+        <v>9.5</v>
       </c>
       <c r="I1023" s="4" t="s">
-        <v>45</v>
+        <v>214</v>
       </c>
       <c r="J1023" s="4">
-        <v>630</v>
+        <v>47.5</v>
       </c>
       <c r="K1023" s="4" t="s">
         <v>25</v>
@@ -42042,23 +42054,23 @@
       <c r="D1024" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E1024" s="5" t="s">
-        <v>212</v>
+      <c r="E1024" s="60" t="s">
+        <v>379</v>
       </c>
       <c r="F1024" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1024" s="4" t="s">
-        <v>213</v>
+        <v>23</v>
       </c>
       <c r="H1024" s="4">
-        <v>9.5</v>
+        <v>25</v>
       </c>
       <c r="I1024" s="4" t="s">
-        <v>214</v>
+        <v>24</v>
       </c>
       <c r="J1024" s="4">
-        <v>47.5</v>
+        <v>50</v>
       </c>
       <c r="K1024" s="4" t="s">
         <v>25</v>
@@ -42072,7 +42084,7 @@
         <v>197</v>
       </c>
       <c r="B1025" s="6">
-        <v>46141</v>
+        <v>46113</v>
       </c>
       <c r="C1025" s="4" t="s">
         <v>14</v>
@@ -42081,22 +42093,22 @@
         <v>198</v>
       </c>
       <c r="E1025" s="5" t="s">
-        <v>244</v>
+        <v>212</v>
       </c>
       <c r="F1025" s="4">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G1025" s="4" t="s">
-        <v>23</v>
+        <v>213</v>
       </c>
       <c r="H1025" s="4">
-        <v>25</v>
+        <v>7.7</v>
       </c>
       <c r="I1025" s="4" t="s">
-        <v>24</v>
+        <v>214</v>
       </c>
       <c r="J1025" s="4">
-        <v>50</v>
+        <v>92.4</v>
       </c>
       <c r="K1025" s="4" t="s">
         <v>25</v>
@@ -42119,22 +42131,22 @@
         <v>198</v>
       </c>
       <c r="E1026" s="5" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="F1026" s="4">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G1026" s="4" t="s">
-        <v>213</v>
+        <v>28</v>
       </c>
       <c r="H1026" s="4">
-        <v>7.7</v>
+        <v>21</v>
       </c>
       <c r="I1026" s="4" t="s">
-        <v>214</v>
+        <v>29</v>
       </c>
       <c r="J1026" s="4">
-        <v>92.4</v>
+        <v>21</v>
       </c>
       <c r="K1026" s="4" t="s">
         <v>25</v>
@@ -42156,23 +42168,23 @@
       <c r="D1027" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E1027" s="5" t="s">
-        <v>199</v>
+      <c r="E1027" s="4" t="s">
+        <v>208</v>
       </c>
       <c r="F1027" s="4">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G1027" s="4" t="s">
         <v>28</v>
       </c>
       <c r="H1027" s="4">
-        <v>21</v>
+        <v>11.3</v>
       </c>
       <c r="I1027" s="4" t="s">
         <v>29</v>
       </c>
       <c r="J1027" s="4">
-        <v>21</v>
+        <v>135.6</v>
       </c>
       <c r="K1027" s="4" t="s">
         <v>25</v>
@@ -42195,22 +42207,22 @@
         <v>198</v>
       </c>
       <c r="E1028" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F1028" s="4">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G1028" s="4" t="s">
-        <v>28</v>
+        <v>210</v>
       </c>
       <c r="H1028" s="4">
-        <v>11.3</v>
+        <v>45</v>
       </c>
       <c r="I1028" s="4" t="s">
-        <v>29</v>
+        <v>211</v>
       </c>
       <c r="J1028" s="4">
-        <v>135.6</v>
+        <v>45</v>
       </c>
       <c r="K1028" s="4" t="s">
         <v>25</v>
@@ -42233,22 +42245,22 @@
         <v>198</v>
       </c>
       <c r="E1029" s="4" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="F1029" s="4">
         <v>1</v>
       </c>
       <c r="G1029" s="4" t="s">
-        <v>210</v>
+        <v>28</v>
       </c>
       <c r="H1029" s="4">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="I1029" s="4" t="s">
-        <v>211</v>
+        <v>29</v>
       </c>
       <c r="J1029" s="4">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="K1029" s="4" t="s">
         <v>25</v>
@@ -42270,23 +42282,23 @@
       <c r="D1030" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E1030" s="4" t="s">
-        <v>205</v>
+      <c r="E1030" s="5" t="s">
+        <v>234</v>
       </c>
       <c r="F1030" s="4">
         <v>1</v>
       </c>
       <c r="G1030" s="4" t="s">
-        <v>28</v>
+        <v>188</v>
       </c>
       <c r="H1030" s="4">
-        <v>15</v>
+        <v>155</v>
       </c>
       <c r="I1030" s="4" t="s">
-        <v>29</v>
+        <v>189</v>
       </c>
       <c r="J1030" s="4">
-        <v>15</v>
+        <v>155</v>
       </c>
       <c r="K1030" s="4" t="s">
         <v>25</v>
@@ -42308,8 +42320,8 @@
       <c r="D1031" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E1031" s="5" t="s">
-        <v>234</v>
+      <c r="E1031" s="60" t="s">
+        <v>590</v>
       </c>
       <c r="F1031" s="4">
         <v>1</v>
@@ -42318,13 +42330,13 @@
         <v>188</v>
       </c>
       <c r="H1031" s="4">
-        <v>155</v>
+        <v>282</v>
       </c>
       <c r="I1031" s="4" t="s">
         <v>189</v>
       </c>
       <c r="J1031" s="4">
-        <v>155</v>
+        <v>282</v>
       </c>
       <c r="K1031" s="4" t="s">
         <v>25</v>
@@ -42347,7 +42359,7 @@
         <v>198</v>
       </c>
       <c r="E1032" s="5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F1032" s="4">
         <v>1</v>
@@ -42356,13 +42368,13 @@
         <v>188</v>
       </c>
       <c r="H1032" s="4">
-        <v>282</v>
+        <v>132</v>
       </c>
       <c r="I1032" s="4" t="s">
         <v>189</v>
       </c>
       <c r="J1032" s="4">
-        <v>282</v>
+        <v>132</v>
       </c>
       <c r="K1032" s="4" t="s">
         <v>25</v>
@@ -42385,22 +42397,22 @@
         <v>198</v>
       </c>
       <c r="E1033" s="5" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="F1033" s="4">
-        <v>1</v>
+        <v>500</v>
       </c>
       <c r="G1033" s="4" t="s">
-        <v>188</v>
+        <v>119</v>
       </c>
       <c r="H1033" s="4">
-        <v>132</v>
+        <v>1.2</v>
       </c>
       <c r="I1033" s="4" t="s">
-        <v>189</v>
+        <v>120</v>
       </c>
       <c r="J1033" s="4">
-        <v>132</v>
+        <v>600</v>
       </c>
       <c r="K1033" s="4" t="s">
         <v>25</v>
@@ -42426,19 +42438,19 @@
         <v>230</v>
       </c>
       <c r="F1034" s="4">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="G1034" s="4" t="s">
         <v>119</v>
       </c>
       <c r="H1034" s="4">
-        <v>1.2</v>
+        <v>1.05</v>
       </c>
       <c r="I1034" s="4" t="s">
         <v>120</v>
       </c>
       <c r="J1034" s="4">
-        <v>600</v>
+        <v>105</v>
       </c>
       <c r="K1034" s="4" t="s">
         <v>25</v>
@@ -42460,23 +42472,23 @@
       <c r="D1035" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E1035" s="5" t="s">
-        <v>230</v>
+      <c r="E1035" s="4" t="s">
+        <v>240</v>
       </c>
       <c r="F1035" s="4">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="G1035" s="4" t="s">
-        <v>119</v>
+        <v>188</v>
       </c>
       <c r="H1035" s="4">
-        <v>1.05</v>
+        <v>114</v>
       </c>
       <c r="I1035" s="4" t="s">
-        <v>120</v>
+        <v>189</v>
       </c>
       <c r="J1035" s="4">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="K1035" s="4" t="s">
         <v>25</v>
@@ -42499,7 +42511,7 @@
         <v>198</v>
       </c>
       <c r="E1036" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F1036" s="4">
         <v>1</v>
@@ -42508,13 +42520,13 @@
         <v>188</v>
       </c>
       <c r="H1036" s="4">
-        <v>114</v>
+        <v>66</v>
       </c>
       <c r="I1036" s="4" t="s">
         <v>189</v>
       </c>
       <c r="J1036" s="4">
-        <v>114</v>
+        <v>66</v>
       </c>
       <c r="K1036" s="4" t="s">
         <v>25</v>
@@ -42537,22 +42549,22 @@
         <v>198</v>
       </c>
       <c r="E1037" s="4" t="s">
-        <v>241</v>
+        <v>201</v>
       </c>
       <c r="F1037" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G1037" s="4" t="s">
-        <v>188</v>
+        <v>28</v>
       </c>
       <c r="H1037" s="4">
-        <v>66</v>
+        <v>0.95</v>
       </c>
       <c r="I1037" s="4" t="s">
-        <v>189</v>
+        <v>29</v>
       </c>
       <c r="J1037" s="4">
-        <v>66</v>
+        <v>9.5</v>
       </c>
       <c r="K1037" s="4" t="s">
         <v>25</v>
@@ -42575,22 +42587,22 @@
         <v>198</v>
       </c>
       <c r="E1038" s="4" t="s">
-        <v>201</v>
+        <v>245</v>
       </c>
       <c r="F1038" s="4">
-        <v>10</v>
-      </c>
-      <c r="G1038" s="4" t="s">
-        <v>28</v>
+        <v>1</v>
+      </c>
+      <c r="G1038" s="60" t="s">
+        <v>188</v>
       </c>
       <c r="H1038" s="4">
-        <v>0.95</v>
+        <v>170</v>
       </c>
       <c r="I1038" s="4" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="J1038" s="4">
-        <v>9.5</v>
+        <v>170</v>
       </c>
       <c r="K1038" s="4" t="s">
         <v>25</v>
@@ -42613,22 +42625,22 @@
         <v>198</v>
       </c>
       <c r="E1039" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F1039" s="4">
         <v>1</v>
       </c>
-      <c r="G1039" s="60" t="s">
-        <v>188</v>
+      <c r="G1039" s="4" t="s">
+        <v>28</v>
       </c>
       <c r="H1039" s="4">
-        <v>170</v>
+        <v>27</v>
       </c>
       <c r="I1039" s="4" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="J1039" s="4">
-        <v>170</v>
+        <v>27</v>
       </c>
       <c r="K1039" s="4" t="s">
         <v>25</v>
@@ -42650,23 +42662,23 @@
       <c r="D1040" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="E1040" s="4" t="s">
-        <v>246</v>
+      <c r="E1040" s="60" t="s">
+        <v>590</v>
       </c>
       <c r="F1040" s="4">
         <v>1</v>
       </c>
       <c r="G1040" s="4" t="s">
-        <v>28</v>
+        <v>188</v>
       </c>
       <c r="H1040" s="4">
-        <v>27</v>
+        <v>282</v>
       </c>
       <c r="I1040" s="4" t="s">
-        <v>29</v>
+        <v>189</v>
       </c>
       <c r="J1040" s="4">
-        <v>27</v>
+        <v>282</v>
       </c>
       <c r="K1040" s="4" t="s">
         <v>25</v>
@@ -42677,7 +42689,7 @@
     </row>
     <row r="1041" spans="1:12">
       <c r="A1041" s="4" t="s">
-        <v>197</v>
+        <v>247</v>
       </c>
       <c r="B1041" s="6">
         <v>46113</v>
@@ -42686,10 +42698,10 @@
         <v>14</v>
       </c>
       <c r="D1041" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="E1041" s="5" t="s">
-        <v>220</v>
+        <v>164</v>
+      </c>
+      <c r="E1041" s="4" t="s">
+        <v>248</v>
       </c>
       <c r="F1041" s="4">
         <v>1</v>
@@ -42698,13 +42710,13 @@
         <v>188</v>
       </c>
       <c r="H1041" s="4">
-        <v>282</v>
+        <v>145</v>
       </c>
       <c r="I1041" s="4" t="s">
         <v>189</v>
       </c>
       <c r="J1041" s="4">
-        <v>282</v>
+        <v>145</v>
       </c>
       <c r="K1041" s="4" t="s">
         <v>25</v>
@@ -42727,22 +42739,22 @@
         <v>164</v>
       </c>
       <c r="E1042" s="4" t="s">
-        <v>248</v>
+        <v>195</v>
       </c>
       <c r="F1042" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1042" s="4" t="s">
         <v>188</v>
       </c>
       <c r="H1042" s="4">
-        <v>145</v>
+        <v>290</v>
       </c>
       <c r="I1042" s="4" t="s">
         <v>189</v>
       </c>
       <c r="J1042" s="4">
-        <v>145</v>
+        <v>0</v>
       </c>
       <c r="K1042" s="4" t="s">
         <v>25</v>
@@ -42756,7 +42768,7 @@
         <v>247</v>
       </c>
       <c r="B1043" s="6">
-        <v>46113</v>
+        <v>46124.6570549429</v>
       </c>
       <c r="C1043" s="4" t="s">
         <v>14</v>
@@ -42765,7 +42777,7 @@
         <v>164</v>
       </c>
       <c r="E1043" s="4" t="s">
-        <v>195</v>
+        <v>248</v>
       </c>
       <c r="F1043" s="4">
         <v>0</v>
@@ -42774,7 +42786,7 @@
         <v>188</v>
       </c>
       <c r="H1043" s="4">
-        <v>290</v>
+        <v>0</v>
       </c>
       <c r="I1043" s="4" t="s">
         <v>189</v>
@@ -42783,7 +42795,7 @@
         <v>0</v>
       </c>
       <c r="K1043" s="4" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="L1043" s="4" t="s">
         <v>20</v>
@@ -42794,7 +42806,7 @@
         <v>247</v>
       </c>
       <c r="B1044" s="6">
-        <v>46124.6570549429</v>
+        <v>46122</v>
       </c>
       <c r="C1044" s="4" t="s">
         <v>14</v>
@@ -42806,22 +42818,22 @@
         <v>248</v>
       </c>
       <c r="F1044" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1044" s="4" t="s">
         <v>188</v>
       </c>
       <c r="H1044" s="4">
-        <v>0</v>
+        <v>145</v>
       </c>
       <c r="I1044" s="4" t="s">
         <v>189</v>
       </c>
       <c r="J1044" s="4">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="K1044" s="4" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="L1044" s="4" t="s">
         <v>20</v>
@@ -42832,7 +42844,7 @@
         <v>247</v>
       </c>
       <c r="B1045" s="6">
-        <v>46122</v>
+        <v>46130</v>
       </c>
       <c r="C1045" s="4" t="s">
         <v>14</v>
@@ -42870,7 +42882,7 @@
         <v>247</v>
       </c>
       <c r="B1046" s="6">
-        <v>46130</v>
+        <v>46124</v>
       </c>
       <c r="C1046" s="4" t="s">
         <v>14</v>
@@ -42882,7 +42894,7 @@
         <v>248</v>
       </c>
       <c r="F1046" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1046" s="4" t="s">
         <v>188</v>
@@ -42894,7 +42906,7 @@
         <v>189</v>
       </c>
       <c r="J1046" s="4">
-        <v>290</v>
+        <v>435</v>
       </c>
       <c r="K1046" s="4" t="s">
         <v>25</v>
@@ -42908,7 +42920,7 @@
         <v>247</v>
       </c>
       <c r="B1047" s="6">
-        <v>46124</v>
+        <v>46121</v>
       </c>
       <c r="C1047" s="4" t="s">
         <v>14</v>
@@ -42920,7 +42932,7 @@
         <v>248</v>
       </c>
       <c r="F1047" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1047" s="4" t="s">
         <v>188</v>
@@ -42932,7 +42944,7 @@
         <v>189</v>
       </c>
       <c r="J1047" s="4">
-        <v>435</v>
+        <v>290</v>
       </c>
       <c r="K1047" s="4" t="s">
         <v>25</v>
@@ -42946,7 +42958,7 @@
         <v>247</v>
       </c>
       <c r="B1048" s="6">
-        <v>46121</v>
+        <v>46138</v>
       </c>
       <c r="C1048" s="4" t="s">
         <v>14</v>
@@ -42981,34 +42993,34 @@
     </row>
     <row r="1049" spans="1:12">
       <c r="A1049" s="4" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B1049" s="6">
-        <v>46138</v>
+        <v>46141</v>
       </c>
       <c r="C1049" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D1049" s="4" t="s">
-        <v>164</v>
+        <v>250</v>
       </c>
       <c r="E1049" s="4" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="F1049" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1049" s="4" t="s">
         <v>188</v>
       </c>
       <c r="H1049" s="4">
-        <v>145</v>
+        <v>128.04</v>
       </c>
       <c r="I1049" s="4" t="s">
         <v>189</v>
       </c>
       <c r="J1049" s="4">
-        <v>290</v>
+        <v>384.12</v>
       </c>
       <c r="K1049" s="4" t="s">
         <v>25</v>
@@ -43031,7 +43043,7 @@
         <v>250</v>
       </c>
       <c r="E1050" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F1050" s="4">
         <v>3</v>
@@ -43040,13 +43052,13 @@
         <v>188</v>
       </c>
       <c r="H1050" s="4">
-        <v>128.04</v>
+        <v>114</v>
       </c>
       <c r="I1050" s="4" t="s">
         <v>189</v>
       </c>
       <c r="J1050" s="4">
-        <v>384.12</v>
+        <v>342</v>
       </c>
       <c r="K1050" s="4" t="s">
         <v>25</v>
@@ -43057,7 +43069,7 @@
     </row>
     <row r="1051" spans="1:12">
       <c r="A1051" s="4" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B1051" s="6">
         <v>46141</v>
@@ -43066,25 +43078,25 @@
         <v>14</v>
       </c>
       <c r="D1051" s="4" t="s">
-        <v>250</v>
+        <v>164</v>
       </c>
       <c r="E1051" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F1051" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1051" s="4" t="s">
         <v>188</v>
       </c>
       <c r="H1051" s="4">
-        <v>114</v>
+        <v>480</v>
       </c>
       <c r="I1051" s="4" t="s">
         <v>189</v>
       </c>
       <c r="J1051" s="4">
-        <v>342</v>
+        <v>960</v>
       </c>
       <c r="K1051" s="4" t="s">
         <v>25</v>
@@ -43098,7 +43110,7 @@
         <v>253</v>
       </c>
       <c r="B1052" s="6">
-        <v>46141</v>
+        <v>46120</v>
       </c>
       <c r="C1052" s="4" t="s">
         <v>14</v>
@@ -43133,34 +43145,34 @@
     </row>
     <row r="1053" spans="1:12">
       <c r="A1053" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B1053" s="6">
-        <v>46120</v>
+        <v>46114</v>
       </c>
       <c r="C1053" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D1053" s="4" t="s">
-        <v>164</v>
+        <v>76</v>
       </c>
       <c r="E1053" s="4" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F1053" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1053" s="4" t="s">
-        <v>188</v>
+        <v>17</v>
       </c>
       <c r="H1053" s="4">
-        <v>480</v>
+        <v>30</v>
       </c>
       <c r="I1053" s="4" t="s">
-        <v>189</v>
+        <v>18</v>
       </c>
       <c r="J1053" s="4">
-        <v>960</v>
+        <v>150</v>
       </c>
       <c r="K1053" s="4" t="s">
         <v>25</v>
@@ -43174,7 +43186,7 @@
         <v>255</v>
       </c>
       <c r="B1054" s="6">
-        <v>46114</v>
+        <v>46126</v>
       </c>
       <c r="C1054" s="4" t="s">
         <v>14</v>
@@ -43212,7 +43224,7 @@
         <v>255</v>
       </c>
       <c r="B1055" s="6">
-        <v>46126</v>
+        <v>46124</v>
       </c>
       <c r="C1055" s="4" t="s">
         <v>14</v>
@@ -43250,7 +43262,7 @@
         <v>255</v>
       </c>
       <c r="B1056" s="6">
-        <v>46124</v>
+        <v>46140</v>
       </c>
       <c r="C1056" s="4" t="s">
         <v>14</v>
@@ -43262,7 +43274,7 @@
         <v>256</v>
       </c>
       <c r="F1056" s="4">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G1056" s="4" t="s">
         <v>17</v>
@@ -43274,7 +43286,7 @@
         <v>18</v>
       </c>
       <c r="J1056" s="4">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="K1056" s="4" t="s">
         <v>25</v>
@@ -43288,7 +43300,7 @@
         <v>255</v>
       </c>
       <c r="B1057" s="6">
-        <v>46140</v>
+        <v>46133</v>
       </c>
       <c r="C1057" s="4" t="s">
         <v>14</v>
@@ -43300,7 +43312,7 @@
         <v>256</v>
       </c>
       <c r="F1057" s="4">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G1057" s="4" t="s">
         <v>17</v>
@@ -43312,7 +43324,7 @@
         <v>18</v>
       </c>
       <c r="J1057" s="4">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="K1057" s="4" t="s">
         <v>25</v>
@@ -43326,7 +43338,7 @@
         <v>255</v>
       </c>
       <c r="B1058" s="6">
-        <v>46133</v>
+        <v>46119</v>
       </c>
       <c r="C1058" s="4" t="s">
         <v>14</v>
@@ -43364,7 +43376,7 @@
         <v>255</v>
       </c>
       <c r="B1059" s="6">
-        <v>46119</v>
+        <v>46115</v>
       </c>
       <c r="C1059" s="4" t="s">
         <v>14</v>
@@ -43402,7 +43414,7 @@
         <v>255</v>
       </c>
       <c r="B1060" s="6">
-        <v>46115</v>
+        <v>46132</v>
       </c>
       <c r="C1060" s="4" t="s">
         <v>14</v>
@@ -43440,7 +43452,7 @@
         <v>255</v>
       </c>
       <c r="B1061" s="6">
-        <v>46132</v>
+        <v>46136</v>
       </c>
       <c r="C1061" s="4" t="s">
         <v>14</v>
@@ -43478,7 +43490,7 @@
         <v>255</v>
       </c>
       <c r="B1062" s="6">
-        <v>46136</v>
+        <v>46128</v>
       </c>
       <c r="C1062" s="4" t="s">
         <v>14</v>
@@ -43513,34 +43525,34 @@
     </row>
     <row r="1063" spans="1:12">
       <c r="A1063" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B1063" s="6">
-        <v>46128</v>
+        <v>46113</v>
       </c>
       <c r="C1063" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D1063" s="4" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="E1063" s="4" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F1063" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1063" s="4" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="H1063" s="4">
+        <v>15</v>
+      </c>
+      <c r="I1063" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="J1063" s="4">
         <v>30</v>
-      </c>
-      <c r="I1063" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="J1063" s="4">
-        <v>150</v>
       </c>
       <c r="K1063" s="4" t="s">
         <v>25</v>
@@ -43554,7 +43566,7 @@
         <v>257</v>
       </c>
       <c r="B1064" s="6">
-        <v>46113</v>
+        <v>46141</v>
       </c>
       <c r="C1064" s="4" t="s">
         <v>14</v>
@@ -43566,7 +43578,7 @@
         <v>258</v>
       </c>
       <c r="F1064" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1064" s="4" t="s">
         <v>31</v>
@@ -43578,7 +43590,7 @@
         <v>259</v>
       </c>
       <c r="J1064" s="4">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="K1064" s="4" t="s">
         <v>25</v>
@@ -43598,25 +43610,25 @@
         <v>14</v>
       </c>
       <c r="D1065" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E1065" s="4" t="s">
-        <v>258</v>
+        <v>250</v>
+      </c>
+      <c r="E1065" s="5" t="s">
+        <v>426</v>
       </c>
       <c r="F1065" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1065" s="4" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="H1065" s="4">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I1065" s="4" t="s">
-        <v>259</v>
+        <v>45</v>
       </c>
       <c r="J1065" s="4">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="K1065" s="4" t="s">
         <v>25</v>
@@ -43630,31 +43642,31 @@
         <v>257</v>
       </c>
       <c r="B1066" s="6">
-        <v>46141</v>
+        <v>46123</v>
       </c>
       <c r="C1066" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D1066" s="4" t="s">
-        <v>250</v>
+        <v>95</v>
       </c>
       <c r="E1066" s="4" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F1066" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1066" s="4" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="H1066" s="4">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="I1066" s="4" t="s">
-        <v>45</v>
+        <v>259</v>
       </c>
       <c r="J1066" s="4">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="K1066" s="4" t="s">
         <v>25</v>
@@ -43677,7 +43689,7 @@
         <v>95</v>
       </c>
       <c r="E1067" s="4" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="F1067" s="4">
         <v>2</v>
@@ -43715,22 +43727,22 @@
         <v>95</v>
       </c>
       <c r="E1068" s="4" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="F1068" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1068" s="4" t="s">
-        <v>31</v>
+        <v>210</v>
       </c>
       <c r="H1068" s="4">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="I1068" s="4" t="s">
-        <v>259</v>
+        <v>211</v>
       </c>
       <c r="J1068" s="4">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K1068" s="4" t="s">
         <v>25</v>
@@ -43750,25 +43762,25 @@
         <v>14</v>
       </c>
       <c r="D1069" s="4" t="s">
-        <v>95</v>
+        <v>164</v>
       </c>
       <c r="E1069" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F1069" s="4">
         <v>1</v>
       </c>
       <c r="G1069" s="4" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
       <c r="H1069" s="4">
-        <v>28</v>
+        <v>540</v>
       </c>
       <c r="I1069" s="4" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="J1069" s="4">
-        <v>28</v>
+        <v>540</v>
       </c>
       <c r="K1069" s="4" t="s">
         <v>25</v>
@@ -43782,31 +43794,31 @@
         <v>257</v>
       </c>
       <c r="B1070" s="6">
-        <v>46123</v>
+        <v>46141</v>
       </c>
       <c r="C1070" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D1070" s="4" t="s">
-        <v>164</v>
+        <v>95</v>
       </c>
       <c r="E1070" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F1070" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1070" s="4" t="s">
-        <v>188</v>
+        <v>210</v>
       </c>
       <c r="H1070" s="4">
-        <v>540</v>
+        <v>28</v>
       </c>
       <c r="I1070" s="4" t="s">
-        <v>189</v>
+        <v>211</v>
       </c>
       <c r="J1070" s="4">
-        <v>540</v>
+        <v>56</v>
       </c>
       <c r="K1070" s="4" t="s">
         <v>25</v>
@@ -43826,25 +43838,25 @@
         <v>14</v>
       </c>
       <c r="D1071" s="4" t="s">
-        <v>95</v>
+        <v>164</v>
       </c>
       <c r="E1071" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="F1071" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1071" s="4" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
       <c r="H1071" s="4">
-        <v>28</v>
+        <v>540</v>
       </c>
       <c r="I1071" s="4" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="J1071" s="4">
-        <v>56</v>
+        <v>540</v>
       </c>
       <c r="K1071" s="4" t="s">
         <v>25</v>
@@ -43858,31 +43870,31 @@
         <v>257</v>
       </c>
       <c r="B1072" s="6">
-        <v>46141</v>
+        <v>46131</v>
       </c>
       <c r="C1072" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D1072" s="4" t="s">
-        <v>164</v>
+        <v>95</v>
       </c>
       <c r="E1072" s="4" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F1072" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1072" s="4" t="s">
-        <v>188</v>
+        <v>31</v>
       </c>
       <c r="H1072" s="4">
-        <v>540</v>
+        <v>15</v>
       </c>
       <c r="I1072" s="4" t="s">
-        <v>189</v>
+        <v>259</v>
       </c>
       <c r="J1072" s="4">
-        <v>540</v>
+        <v>30</v>
       </c>
       <c r="K1072" s="4" t="s">
         <v>25</v>
@@ -43902,25 +43914,25 @@
         <v>14</v>
       </c>
       <c r="D1073" s="4" t="s">
-        <v>95</v>
+        <v>250</v>
       </c>
       <c r="E1073" s="4" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F1073" s="4">
         <v>2</v>
       </c>
       <c r="G1073" s="4" t="s">
-        <v>31</v>
+        <v>188</v>
       </c>
       <c r="H1073" s="4">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="I1073" s="4" t="s">
-        <v>259</v>
+        <v>189</v>
       </c>
       <c r="J1073" s="4">
-        <v>30</v>
+        <v>140</v>
       </c>
       <c r="K1073" s="4" t="s">
         <v>25</v>
@@ -43940,25 +43952,25 @@
         <v>14</v>
       </c>
       <c r="D1074" s="4" t="s">
-        <v>250</v>
+        <v>164</v>
       </c>
       <c r="E1074" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F1074" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1074" s="4" t="s">
         <v>188</v>
       </c>
       <c r="H1074" s="4">
-        <v>70</v>
+        <v>540</v>
       </c>
       <c r="I1074" s="4" t="s">
         <v>189</v>
       </c>
       <c r="J1074" s="4">
-        <v>140</v>
+        <v>540</v>
       </c>
       <c r="K1074" s="4" t="s">
         <v>25</v>
@@ -43972,31 +43984,31 @@
         <v>257</v>
       </c>
       <c r="B1075" s="6">
-        <v>46131</v>
+        <v>46113</v>
       </c>
       <c r="C1075" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D1075" s="4" t="s">
-        <v>164</v>
+        <v>95</v>
       </c>
       <c r="E1075" s="4" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F1075" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1075" s="4" t="s">
-        <v>188</v>
+        <v>31</v>
       </c>
       <c r="H1075" s="4">
-        <v>540</v>
+        <v>15</v>
       </c>
       <c r="I1075" s="4" t="s">
-        <v>189</v>
+        <v>259</v>
       </c>
       <c r="J1075" s="4">
-        <v>540</v>
+        <v>30</v>
       </c>
       <c r="K1075" s="4" t="s">
         <v>25</v>
@@ -44016,25 +44028,25 @@
         <v>14</v>
       </c>
       <c r="D1076" s="4" t="s">
-        <v>95</v>
+        <v>250</v>
       </c>
       <c r="E1076" s="4" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F1076" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1076" s="4" t="s">
-        <v>31</v>
+        <v>188</v>
       </c>
       <c r="H1076" s="4">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="I1076" s="4" t="s">
-        <v>259</v>
+        <v>189</v>
       </c>
       <c r="J1076" s="4">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="K1076" s="4" t="s">
         <v>25</v>
@@ -44056,23 +44068,23 @@
       <c r="D1077" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="E1077" s="4" t="s">
-        <v>264</v>
+      <c r="E1077" s="5" t="s">
+        <v>426</v>
       </c>
       <c r="F1077" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1077" s="4" t="s">
-        <v>188</v>
+        <v>44</v>
       </c>
       <c r="H1077" s="4">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="I1077" s="4" t="s">
-        <v>189</v>
+        <v>45</v>
       </c>
       <c r="J1077" s="4">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="K1077" s="4" t="s">
         <v>25</v>
@@ -44092,25 +44104,25 @@
         <v>14</v>
       </c>
       <c r="D1078" s="4" t="s">
-        <v>250</v>
+        <v>164</v>
       </c>
       <c r="E1078" s="4" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="F1078" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1078" s="4" t="s">
-        <v>44</v>
+        <v>188</v>
       </c>
       <c r="H1078" s="4">
-        <v>18</v>
+        <v>540</v>
       </c>
       <c r="I1078" s="4" t="s">
-        <v>45</v>
+        <v>189</v>
       </c>
       <c r="J1078" s="4">
-        <v>90</v>
+        <v>540</v>
       </c>
       <c r="K1078" s="4" t="s">
         <v>25</v>
@@ -44121,10 +44133,10 @@
     </row>
     <row r="1079" spans="1:12">
       <c r="A1079" s="4" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="B1079" s="6">
-        <v>46113</v>
+        <v>46136</v>
       </c>
       <c r="C1079" s="4" t="s">
         <v>14</v>
@@ -44133,7 +44145,7 @@
         <v>164</v>
       </c>
       <c r="E1079" s="4" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F1079" s="4">
         <v>1</v>
@@ -44142,13 +44154,13 @@
         <v>188</v>
       </c>
       <c r="H1079" s="4">
-        <v>540</v>
+        <v>350</v>
       </c>
       <c r="I1079" s="4" t="s">
         <v>189</v>
       </c>
       <c r="J1079" s="4">
-        <v>540</v>
+        <v>350</v>
       </c>
       <c r="K1079" s="4" t="s">
         <v>25</v>
@@ -44162,7 +44174,7 @@
         <v>265</v>
       </c>
       <c r="B1080" s="6">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="C1080" s="4" t="s">
         <v>14</v>
@@ -44171,22 +44183,22 @@
         <v>164</v>
       </c>
       <c r="E1080" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F1080" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1080" s="4" t="s">
         <v>188</v>
       </c>
       <c r="H1080" s="4">
-        <v>350</v>
+        <v>600</v>
       </c>
       <c r="I1080" s="4" t="s">
         <v>189</v>
       </c>
       <c r="J1080" s="4">
-        <v>350</v>
+        <v>1800</v>
       </c>
       <c r="K1080" s="4" t="s">
         <v>25</v>
@@ -44206,25 +44218,25 @@
         <v>14</v>
       </c>
       <c r="D1081" s="4" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="E1081" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F1081" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1081" s="4" t="s">
         <v>188</v>
       </c>
       <c r="H1081" s="4">
-        <v>600</v>
+        <v>255</v>
       </c>
       <c r="I1081" s="4" t="s">
         <v>189</v>
       </c>
       <c r="J1081" s="4">
-        <v>1800</v>
+        <v>510</v>
       </c>
       <c r="K1081" s="4" t="s">
         <v>25</v>
@@ -44238,7 +44250,7 @@
         <v>265</v>
       </c>
       <c r="B1082" s="6">
-        <v>46137</v>
+        <v>46114</v>
       </c>
       <c r="C1082" s="4" t="s">
         <v>14</v>
@@ -44282,25 +44294,25 @@
         <v>14</v>
       </c>
       <c r="D1083" s="4" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="E1083" s="4" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F1083" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1083" s="4" t="s">
         <v>188</v>
       </c>
       <c r="H1083" s="4">
-        <v>255</v>
+        <v>350</v>
       </c>
       <c r="I1083" s="4" t="s">
         <v>189</v>
       </c>
       <c r="J1083" s="4">
-        <v>510</v>
+        <v>350</v>
       </c>
       <c r="K1083" s="4" t="s">
         <v>25</v>
@@ -44323,7 +44335,7 @@
         <v>164</v>
       </c>
       <c r="E1084" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F1084" s="4">
         <v>1</v>
@@ -44332,13 +44344,13 @@
         <v>188</v>
       </c>
       <c r="H1084" s="4">
-        <v>350</v>
+        <v>600</v>
       </c>
       <c r="I1084" s="4" t="s">
         <v>189</v>
       </c>
       <c r="J1084" s="4">
-        <v>350</v>
+        <v>600</v>
       </c>
       <c r="K1084" s="4" t="s">
         <v>25</v>
@@ -44349,34 +44361,34 @@
     </row>
     <row r="1085" spans="1:12">
       <c r="A1085" s="4" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B1085" s="6">
-        <v>46114</v>
+        <v>46113</v>
       </c>
       <c r="C1085" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D1085" s="4" t="s">
-        <v>164</v>
+        <v>70</v>
       </c>
       <c r="E1085" s="4" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F1085" s="4">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G1085" s="4" t="s">
-        <v>188</v>
+        <v>17</v>
       </c>
       <c r="H1085" s="4">
-        <v>600</v>
+        <v>23</v>
       </c>
       <c r="I1085" s="4" t="s">
-        <v>189</v>
+        <v>18</v>
       </c>
       <c r="J1085" s="4">
-        <v>600</v>
+        <v>2300</v>
       </c>
       <c r="K1085" s="4" t="s">
         <v>25</v>
@@ -44396,25 +44408,25 @@
         <v>14</v>
       </c>
       <c r="D1086" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="E1086" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F1086" s="4">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="G1086" s="4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="H1086" s="4">
-        <v>23</v>
+        <v>16.8</v>
       </c>
       <c r="I1086" s="4" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J1086" s="4">
-        <v>2300</v>
+        <v>33.6</v>
       </c>
       <c r="K1086" s="4" t="s">
         <v>25</v>
@@ -44434,25 +44446,25 @@
         <v>14</v>
       </c>
       <c r="D1087" s="4" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="E1087" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F1087" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1087" s="4" t="s">
-        <v>23</v>
+        <v>188</v>
       </c>
       <c r="H1087" s="4">
-        <v>16.8</v>
+        <v>390</v>
       </c>
       <c r="I1087" s="4" t="s">
-        <v>24</v>
+        <v>189</v>
       </c>
       <c r="J1087" s="4">
-        <v>33.6</v>
+        <v>390</v>
       </c>
       <c r="K1087" s="4" t="s">
         <v>25</v>
@@ -44475,22 +44487,22 @@
         <v>95</v>
       </c>
       <c r="E1088" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F1088" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G1088" s="4" t="s">
-        <v>188</v>
+        <v>34</v>
       </c>
       <c r="H1088" s="4">
-        <v>390</v>
+        <v>2</v>
       </c>
       <c r="I1088" s="4" t="s">
-        <v>189</v>
+        <v>36</v>
       </c>
       <c r="J1088" s="4">
-        <v>390</v>
+        <v>20</v>
       </c>
       <c r="K1088" s="4" t="s">
         <v>25</v>
@@ -44499,7 +44511,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1089" spans="1:12">
+    <row r="1089" spans="1:13">
       <c r="A1089" s="4" t="s">
         <v>269</v>
       </c>
@@ -44513,22 +44525,22 @@
         <v>95</v>
       </c>
       <c r="E1089" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F1089" s="4">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G1089" s="4" t="s">
-        <v>34</v>
+        <v>210</v>
       </c>
       <c r="H1089" s="4">
-        <v>2</v>
+        <v>33.7</v>
       </c>
       <c r="I1089" s="4" t="s">
-        <v>36</v>
+        <v>211</v>
       </c>
       <c r="J1089" s="4">
-        <v>20</v>
+        <v>67.4</v>
       </c>
       <c r="K1089" s="4" t="s">
         <v>25</v>
@@ -44536,8 +44548,11 @@
       <c r="L1089" s="4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="1090" spans="1:13">
+      <c r="M1089" s="61" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:12">
       <c r="A1090" s="4" t="s">
         <v>269</v>
       </c>
@@ -44551,31 +44566,28 @@
         <v>95</v>
       </c>
       <c r="E1090" s="4" t="s">
-        <v>274</v>
+        <v>174</v>
       </c>
       <c r="F1090" s="4">
-        <v>2</v>
-      </c>
-      <c r="G1090" s="4" t="s">
-        <v>210</v>
+        <v>8</v>
+      </c>
+      <c r="G1090" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="H1090" s="4">
-        <v>33.7</v>
+        <v>5</v>
       </c>
       <c r="I1090" s="4" t="s">
-        <v>211</v>
+        <v>18</v>
       </c>
       <c r="J1090" s="4">
-        <v>67.4</v>
+        <v>40</v>
       </c>
       <c r="K1090" s="4" t="s">
         <v>25</v>
       </c>
       <c r="L1090" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="M1090" s="61" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="1091" spans="1:12">
@@ -44592,22 +44604,22 @@
         <v>95</v>
       </c>
       <c r="E1091" s="4" t="s">
-        <v>174</v>
+        <v>275</v>
       </c>
       <c r="F1091" s="4">
-        <v>8</v>
-      </c>
-      <c r="G1091" s="5" t="s">
-        <v>23</v>
+        <v>1</v>
+      </c>
+      <c r="G1091" s="4" t="s">
+        <v>210</v>
       </c>
       <c r="H1091" s="4">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="I1091" s="4" t="s">
-        <v>18</v>
+        <v>211</v>
       </c>
       <c r="J1091" s="4">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="K1091" s="4" t="s">
         <v>25</v>
@@ -44630,22 +44642,22 @@
         <v>95</v>
       </c>
       <c r="E1092" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F1092" s="4">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G1092" s="4" t="s">
-        <v>210</v>
+        <v>34</v>
       </c>
       <c r="H1092" s="4">
-        <v>76</v>
+        <v>1.18</v>
       </c>
       <c r="I1092" s="4" t="s">
-        <v>211</v>
+        <v>36</v>
       </c>
       <c r="J1092" s="4">
-        <v>76</v>
+        <v>11.8</v>
       </c>
       <c r="K1092" s="4" t="s">
         <v>25</v>
@@ -44668,22 +44680,22 @@
         <v>95</v>
       </c>
       <c r="E1093" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F1093" s="4">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G1093" s="4" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="H1093" s="4">
-        <v>1.18</v>
+        <v>5</v>
       </c>
       <c r="I1093" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="J1093" s="4">
-        <v>11.8</v>
+        <v>60</v>
       </c>
       <c r="K1093" s="4" t="s">
         <v>25</v>
@@ -44706,22 +44718,22 @@
         <v>95</v>
       </c>
       <c r="E1094" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F1094" s="4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G1094" s="4" t="s">
         <v>23</v>
       </c>
       <c r="H1094" s="4">
-        <v>5</v>
+        <v>16.38</v>
       </c>
       <c r="I1094" s="4" t="s">
         <v>24</v>
       </c>
       <c r="J1094" s="4">
-        <v>60</v>
+        <v>98.28</v>
       </c>
       <c r="K1094" s="4" t="s">
         <v>25</v>
@@ -44744,22 +44756,22 @@
         <v>95</v>
       </c>
       <c r="E1095" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F1095" s="4">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1095" s="4" t="s">
         <v>23</v>
       </c>
       <c r="H1095" s="4">
-        <v>16.38</v>
+        <v>13</v>
       </c>
       <c r="I1095" s="4" t="s">
         <v>24</v>
       </c>
       <c r="J1095" s="4">
-        <v>98.28</v>
+        <v>39</v>
       </c>
       <c r="K1095" s="4" t="s">
         <v>25</v>
@@ -44782,22 +44794,22 @@
         <v>95</v>
       </c>
       <c r="E1096" s="4" t="s">
-        <v>279</v>
+        <v>172</v>
       </c>
       <c r="F1096" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1096" s="4" t="s">
         <v>23</v>
       </c>
       <c r="H1096" s="4">
-        <v>13</v>
+        <v>3.58</v>
       </c>
       <c r="I1096" s="4" t="s">
         <v>24</v>
       </c>
       <c r="J1096" s="4">
-        <v>39</v>
+        <v>17.9</v>
       </c>
       <c r="K1096" s="4" t="s">
         <v>25</v>
@@ -44817,10 +44829,10 @@
         <v>14</v>
       </c>
       <c r="D1097" s="4" t="s">
-        <v>95</v>
+        <v>145</v>
       </c>
       <c r="E1097" s="4" t="s">
-        <v>172</v>
+        <v>280</v>
       </c>
       <c r="F1097" s="4">
         <v>5</v>
@@ -44829,13 +44841,13 @@
         <v>23</v>
       </c>
       <c r="H1097" s="4">
-        <v>3.58</v>
+        <v>12.56</v>
       </c>
       <c r="I1097" s="4" t="s">
         <v>24</v>
       </c>
       <c r="J1097" s="4">
-        <v>17.9</v>
+        <v>62.8</v>
       </c>
       <c r="K1097" s="4" t="s">
         <v>25</v>
@@ -44857,23 +44869,23 @@
       <c r="D1098" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="E1098" s="4" t="s">
-        <v>280</v>
+      <c r="E1098" s="5" t="s">
+        <v>281</v>
       </c>
       <c r="F1098" s="4">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G1098" s="4" t="s">
-        <v>23</v>
+        <v>210</v>
       </c>
       <c r="H1098" s="4">
-        <v>12.56</v>
+        <v>101</v>
       </c>
       <c r="I1098" s="4" t="s">
-        <v>24</v>
+        <v>211</v>
       </c>
       <c r="J1098" s="4">
-        <v>62.8</v>
+        <v>1212</v>
       </c>
       <c r="K1098" s="4" t="s">
         <v>25</v>
@@ -44895,23 +44907,23 @@
       <c r="D1099" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="E1099" s="5" t="s">
-        <v>281</v>
+      <c r="E1099" s="4" t="s">
+        <v>282</v>
       </c>
       <c r="F1099" s="4">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G1099" s="4" t="s">
         <v>210</v>
       </c>
       <c r="H1099" s="4">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="I1099" s="4" t="s">
         <v>211</v>
       </c>
       <c r="J1099" s="4">
-        <v>1212</v>
+        <v>75</v>
       </c>
       <c r="K1099" s="4" t="s">
         <v>25</v>
@@ -44931,25 +44943,25 @@
         <v>14</v>
       </c>
       <c r="D1100" s="4" t="s">
-        <v>145</v>
+        <v>95</v>
       </c>
       <c r="E1100" s="4" t="s">
-        <v>282</v>
+        <v>109</v>
       </c>
       <c r="F1100" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G1100" s="4" t="s">
-        <v>210</v>
+        <v>23</v>
       </c>
       <c r="H1100" s="4">
-        <v>75</v>
+        <v>7.85</v>
       </c>
       <c r="I1100" s="4" t="s">
-        <v>211</v>
+        <v>24</v>
       </c>
       <c r="J1100" s="4">
-        <v>75</v>
+        <v>47.1</v>
       </c>
       <c r="K1100" s="4" t="s">
         <v>25</v>
@@ -44972,22 +44984,22 @@
         <v>95</v>
       </c>
       <c r="E1101" s="4" t="s">
-        <v>109</v>
+        <v>177</v>
       </c>
       <c r="F1101" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1101" s="4" t="s">
         <v>23</v>
       </c>
       <c r="H1101" s="4">
-        <v>7.85</v>
+        <v>13</v>
       </c>
       <c r="I1101" s="4" t="s">
         <v>24</v>
       </c>
       <c r="J1101" s="4">
-        <v>47.1</v>
+        <v>52</v>
       </c>
       <c r="K1101" s="4" t="s">
         <v>25</v>
@@ -45010,22 +45022,22 @@
         <v>95</v>
       </c>
       <c r="E1102" s="4" t="s">
-        <v>177</v>
+        <v>283</v>
       </c>
       <c r="F1102" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1102" s="4" t="s">
         <v>23</v>
       </c>
       <c r="H1102" s="4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="I1102" s="4" t="s">
         <v>24</v>
       </c>
       <c r="J1102" s="4">
-        <v>52</v>
+        <v>13.5</v>
       </c>
       <c r="K1102" s="4" t="s">
         <v>25</v>
@@ -45048,22 +45060,22 @@
         <v>95</v>
       </c>
       <c r="E1103" s="4" t="s">
-        <v>283</v>
+        <v>175</v>
       </c>
       <c r="F1103" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G1103" s="4" t="s">
         <v>23</v>
       </c>
       <c r="H1103" s="4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="I1103" s="4" t="s">
         <v>24</v>
       </c>
       <c r="J1103" s="4">
-        <v>13.5</v>
+        <v>65</v>
       </c>
       <c r="K1103" s="4" t="s">
         <v>25</v>
@@ -45077,31 +45089,31 @@
         <v>269</v>
       </c>
       <c r="B1104" s="6">
-        <v>46113</v>
+        <v>46131</v>
       </c>
       <c r="C1104" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D1104" s="4" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="E1104" s="4" t="s">
-        <v>175</v>
+        <v>271</v>
       </c>
       <c r="F1104" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1104" s="4" t="s">
         <v>23</v>
       </c>
       <c r="H1104" s="4">
-        <v>13</v>
+        <v>16.8</v>
       </c>
       <c r="I1104" s="4" t="s">
         <v>24</v>
       </c>
       <c r="J1104" s="4">
-        <v>65</v>
+        <v>33.6</v>
       </c>
       <c r="K1104" s="4" t="s">
         <v>25</v>
@@ -45121,10 +45133,10 @@
         <v>14</v>
       </c>
       <c r="D1105" s="4" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="E1105" s="4" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="F1105" s="4">
         <v>2</v>
@@ -45133,13 +45145,13 @@
         <v>23</v>
       </c>
       <c r="H1105" s="4">
-        <v>16.8</v>
+        <v>62</v>
       </c>
       <c r="I1105" s="4" t="s">
         <v>24</v>
       </c>
       <c r="J1105" s="4">
-        <v>33.6</v>
+        <v>124</v>
       </c>
       <c r="K1105" s="4" t="s">
         <v>25</v>
@@ -45148,7 +45160,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="1106" spans="1:12">
+    <row r="1106" spans="1:13">
       <c r="A1106" s="4" t="s">
         <v>269</v>
       </c>
@@ -45162,22 +45174,22 @@
         <v>95</v>
       </c>
       <c r="E1106" s="4" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="F1106" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1106" s="4" t="s">
-        <v>23</v>
+        <v>210</v>
       </c>
       <c r="H1106" s="4">
-        <v>62</v>
+        <v>33.7</v>
       </c>
       <c r="I1106" s="4" t="s">
-        <v>24</v>
+        <v>211</v>
       </c>
       <c r="J1106" s="4">
-        <v>124</v>
+        <v>33.7</v>
       </c>
       <c r="K1106" s="4" t="s">
         <v>25</v>
@@ -45185,8 +45197,11 @@
       <c r="L1106" s="4" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="1107" spans="1:13">
+      <c r="M1106" s="61" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:12">
       <c r="A1107" s="4" t="s">
         <v>269</v>
       </c>
@@ -45200,31 +45215,28 @@
         <v>95</v>
       </c>
       <c r="E1107" s="4" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="F1107" s="4">
         <v>1</v>
       </c>
       <c r="G1107" s="4" t="s">
-        <v>210</v>
+        <v>23</v>
       </c>
       <c r="H1107" s="4">
-        <v>33.7</v>
+        <v>92</v>
       </c>
       <c r="I1107" s="4" t="s">
-        <v>211</v>
+        <v>24</v>
       </c>
       <c r="J1107" s="4">
-        <v>33.7</v>
+        <v>92</v>
       </c>
       <c r="K1107" s="4" t="s">
         <v>25</v>
       </c>
       <c r="L1107" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="M1107" s="61" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="1108" spans="1:12">
@@ -45241,22 +45253,22 @@
         <v>95</v>
       </c>
       <c r="E1108" s="4" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="F1108" s="4">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G1108" s="4" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="H1108" s="4">
-        <v>92</v>
+        <v>1.18</v>
       </c>
       <c r="I1108" s="4" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="J1108" s="4">
-        <v>92</v>
+        <v>9.44</v>
       </c>
       <c r="K1108" s="4" t="s">
         <v>25</v>
@@ -45279,22 +45291,22 @@
         <v>95</v>
       </c>
       <c r="E1109" s="4" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F1109" s="4">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G1109" s="4" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="H1109" s="4">
-        <v>1.18</v>
+        <v>5</v>
       </c>
       <c r="I1109" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="J1109" s="4">
-        <v>9.44</v>
+        <v>60</v>
       </c>
       <c r="K1109" s="4" t="s">
         <v>25</v>
@@ -45317,22 +45329,22 @@
         <v>95</v>
       </c>
       <c r="E1110" s="4" t="s">
-        <v>277</v>
+        <v>172</v>
       </c>
       <c r="F1110" s="4">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G1110" s="4" t="s">
         <v>23</v>
       </c>
       <c r="H1110" s="4">
-        <v>5</v>
+        <v>3.58</v>
       </c>
       <c r="I1110" s="4" t="s">
         <v>24</v>
       </c>
       <c r="J1110" s="4">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K1110" s="4" t="s">
         <v>25</v>
@@ -45352,25 +45364,25 @@
         <v>14</v>
       </c>
       <c r="D1111" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E1111" s="4" t="s">
-        <v>172</v>
+        <v>145</v>
+      </c>
+      <c r="E1111" s="5" t="s">
+        <v>281</v>
       </c>
       <c r="F1111" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G1111" s="4" t="s">
-        <v>23</v>
+        <v>210</v>
       </c>
       <c r="H1111" s="4">
-        <v>3.58</v>
+        <v>101</v>
       </c>
       <c r="I1111" s="4" t="s">
-        <v>24</v>
+        <v>211</v>
       </c>
       <c r="J1111" s="4">
-        <v>0</v>
+        <v>1010</v>
       </c>
       <c r="K1111" s="4" t="s">
         <v>25</v>
@@ -45384,34 +45396,34 @@
         <v>269</v>
       </c>
       <c r="B1112" s="6">
-        <v>46131</v>
+        <v>46113.6605566871</v>
       </c>
       <c r="C1112" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D1112" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="E1112" s="5" t="s">
-        <v>281</v>
+        <v>95</v>
+      </c>
+      <c r="E1112" s="4" t="s">
+        <v>109</v>
       </c>
       <c r="F1112" s="4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G1112" s="4" t="s">
-        <v>210</v>
+        <v>23</v>
       </c>
       <c r="H1112" s="4">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="I1112" s="4" t="s">
-        <v>211</v>
+        <v>24</v>
       </c>
       <c r="J1112" s="4">
-        <v>1010</v>
+        <v>0</v>
       </c>
       <c r="K1112" s="4" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="L1112" s="4" t="s">
         <v>20</v>
@@ -45431,7 +45443,7 @@
         <v>95</v>
       </c>
       <c r="E1113" s="4" t="s">
-        <v>109</v>
+        <v>177</v>
       </c>
       <c r="F1113" s="4">
         <v>0</v>
@@ -45469,7 +45481,7 @@
         <v>95</v>
       </c>
       <c r="E1114" s="4" t="s">
-        <v>177</v>
+        <v>283</v>
       </c>
       <c r="F1114" s="4">
         <v>0</v>
@@ -45507,7 +45519,7 @@
         <v>95</v>
       </c>
       <c r="E1115" s="4" t="s">
-        <v>283</v>
+        <v>175</v>
       </c>
       <c r="F1115" s="4">
         <v>0</v>
@@ -45536,7 +45548,7 @@
         <v>269</v>
       </c>
       <c r="B1116" s="6">
-        <v>46113.6605566871</v>
+        <v>46121</v>
       </c>
       <c r="C1116" s="4" t="s">
         <v>14</v>
@@ -45545,25 +45557,25 @@
         <v>95</v>
       </c>
       <c r="E1116" s="4" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F1116" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G1116" s="4" t="s">
         <v>23</v>
       </c>
       <c r="H1116" s="4">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I1116" s="4" t="s">
         <v>24</v>
       </c>
       <c r="J1116" s="4">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="K1116" s="4" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="L1116" s="4" t="s">
         <v>20</v>
@@ -45583,22 +45595,22 @@
         <v>95</v>
       </c>
       <c r="E1117" s="4" t="s">
-        <v>177</v>
+        <v>272</v>
       </c>
       <c r="F1117" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1117" s="4" t="s">
-        <v>23</v>
+        <v>188</v>
       </c>
       <c r="H1117" s="4">
-        <v>13</v>
+        <v>390</v>
       </c>
       <c r="I1117" s="4" t="s">
-        <v>24</v>
+        <v>189</v>
       </c>
       <c r="J1117" s="4">
-        <v>52</v>
+        <v>780</v>
       </c>
       <c r="K1117" s="4" t="s">
         <v>25</v>
@@ -45621,22 +45633,22 @@
         <v>95</v>
       </c>
       <c r="E1118" s="4" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="F1118" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1118" s="4" t="s">
-        <v>188</v>
+        <v>17</v>
       </c>
       <c r="H1118" s="4">
-        <v>390</v>
+        <v>15</v>
       </c>
       <c r="I1118" s="4" t="s">
-        <v>189</v>
+        <v>18</v>
       </c>
       <c r="J1118" s="4">
-        <v>780</v>
+        <v>15</v>
       </c>
       <c r="K1118" s="4" t="s">
         <v>25</v>
@@ -45659,22 +45671,22 @@
         <v>95</v>
       </c>
       <c r="E1119" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F1119" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1119" s="4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="H1119" s="4">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I1119" s="4" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J1119" s="4">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K1119" s="4" t="s">
         <v>25</v>
@@ -45697,22 +45709,22 @@
         <v>95</v>
       </c>
       <c r="E1120" s="4" t="s">
-        <v>287</v>
+        <v>109</v>
       </c>
       <c r="F1120" s="4">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G1120" s="4" t="s">
         <v>23</v>
       </c>
       <c r="H1120" s="4">
-        <v>9</v>
+        <v>7.85</v>
       </c>
       <c r="I1120" s="4" t="s">
         <v>24</v>
       </c>
       <c r="J1120" s="4">
-        <v>18</v>
+        <v>94.2</v>
       </c>
       <c r="K1120" s="4" t="s">
         <v>25</v>
@@ -45735,22 +45747,22 @@
         <v>95</v>
       </c>
       <c r="E1121" s="4" t="s">
-        <v>109</v>
+        <v>288</v>
       </c>
       <c r="F1121" s="4">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="G1121" s="4" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H1121" s="4">
-        <v>7.85</v>
+        <v>16</v>
       </c>
       <c r="I1121" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J1121" s="4">
-        <v>94.2</v>
+        <v>16</v>
       </c>
       <c r="K1121" s="4" t="s">
         <v>25</v>
@@ -45773,22 +45785,22 @@
         <v>95</v>
       </c>
       <c r="E1122" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F1122" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1122" s="4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="H1122" s="4">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I1122" s="4" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J1122" s="4">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="K1122" s="4" t="s">
         <v>25</v>
@@ -45811,22 +45823,22 @@
         <v>95</v>
       </c>
       <c r="E1123" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F1123" s="4">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G1123" s="4" t="s">
         <v>23</v>
       </c>
       <c r="H1123" s="4">
-        <v>18</v>
+        <v>3.58</v>
       </c>
       <c r="I1123" s="4" t="s">
         <v>24</v>
       </c>
       <c r="J1123" s="4">
-        <v>72</v>
+        <v>42.96</v>
       </c>
       <c r="K1123" s="4" t="s">
         <v>25</v>
@@ -45849,22 +45861,22 @@
         <v>95</v>
       </c>
       <c r="E1124" s="4" t="s">
-        <v>290</v>
+        <v>110</v>
       </c>
       <c r="F1124" s="4">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G1124" s="4" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="H1124" s="4">
-        <v>3.58</v>
+        <v>7</v>
       </c>
       <c r="I1124" s="4" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J1124" s="4">
-        <v>42.96</v>
+        <v>56</v>
       </c>
       <c r="K1124" s="4" t="s">
         <v>25</v>
@@ -45887,22 +45899,22 @@
         <v>95</v>
       </c>
       <c r="E1125" s="4" t="s">
-        <v>110</v>
+        <v>174</v>
       </c>
       <c r="F1125" s="4">
         <v>8</v>
       </c>
-      <c r="G1125" s="4" t="s">
-        <v>17</v>
+      <c r="G1125" s="5" t="s">
+        <v>23</v>
       </c>
       <c r="H1125" s="4">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I1125" s="4" t="s">
         <v>18</v>
       </c>
       <c r="J1125" s="4">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="K1125" s="4" t="s">
         <v>25</v>
@@ -45925,22 +45937,22 @@
         <v>95</v>
       </c>
       <c r="E1126" s="4" t="s">
-        <v>174</v>
+        <v>291</v>
       </c>
       <c r="F1126" s="4">
-        <v>8</v>
-      </c>
-      <c r="G1126" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1126" s="4" t="s">
         <v>23</v>
       </c>
       <c r="H1126" s="4">
         <v>5</v>
       </c>
       <c r="I1126" s="4" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J1126" s="4">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="K1126" s="4" t="s">
         <v>25</v>
@@ -45963,10 +45975,10 @@
         <v>95</v>
       </c>
       <c r="E1127" s="4" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="F1127" s="4">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="G1127" s="4" t="s">
         <v>23</v>
@@ -45978,7 +45990,7 @@
         <v>24</v>
       </c>
       <c r="J1127" s="4">
-        <v>10</v>
+        <v>120</v>
       </c>
       <c r="K1127" s="4" t="s">
         <v>25</v>
@@ -46001,22 +46013,22 @@
         <v>95</v>
       </c>
       <c r="E1128" s="4" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F1128" s="4">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="G1128" s="4" t="s">
         <v>23</v>
       </c>
       <c r="H1128" s="4">
-        <v>5</v>
+        <v>16.38</v>
       </c>
       <c r="I1128" s="4" t="s">
         <v>24</v>
       </c>
       <c r="J1128" s="4">
-        <v>120</v>
+        <v>98.28</v>
       </c>
       <c r="K1128" s="4" t="s">
         <v>25</v>
@@ -46039,7 +46051,7 @@
         <v>95</v>
       </c>
       <c r="E1129" s="4" t="s">
-        <v>278</v>
+        <v>175</v>
       </c>
       <c r="F1129" s="4">
         <v>6</v>
@@ -46048,13 +46060,13 @@
         <v>23</v>
       </c>
       <c r="H1129" s="4">
-        <v>16.38</v>
+        <v>13</v>
       </c>
       <c r="I1129" s="4" t="s">
         <v>24</v>
       </c>
       <c r="J1129" s="4">
-        <v>98.28</v>
+        <v>78</v>
       </c>
       <c r="K1129" s="4" t="s">
         <v>25</v>
@@ -46077,10 +46089,10 @@
         <v>95</v>
       </c>
       <c r="E1130" s="4" t="s">
-        <v>175</v>
+        <v>279</v>
       </c>
       <c r="F1130" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1130" s="4" t="s">
         <v>23</v>
@@ -46092,7 +46104,7 @@
         <v>24</v>
       </c>
       <c r="J1130" s="4">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="K1130" s="4" t="s">
         <v>25</v>
@@ -46115,22 +46127,22 @@
         <v>95</v>
       </c>
       <c r="E1131" s="4" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="F1131" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1131" s="4" t="s">
         <v>23</v>
       </c>
       <c r="H1131" s="4">
-        <v>13</v>
+        <v>4.82</v>
       </c>
       <c r="I1131" s="4" t="s">
         <v>24</v>
       </c>
       <c r="J1131" s="4">
-        <v>52</v>
+        <v>14.46</v>
       </c>
       <c r="K1131" s="4" t="s">
         <v>25</v>
@@ -46153,22 +46165,22 @@
         <v>95</v>
       </c>
       <c r="E1132" s="4" t="s">
-        <v>292</v>
+        <v>172</v>
       </c>
       <c r="F1132" s="4">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="G1132" s="4" t="s">
         <v>23</v>
       </c>
       <c r="H1132" s="4">
-        <v>4.82</v>
+        <v>3.58</v>
       </c>
       <c r="I1132" s="4" t="s">
         <v>24</v>
       </c>
       <c r="J1132" s="4">
-        <v>14.46</v>
+        <v>25.06</v>
       </c>
       <c r="K1132" s="4" t="s">
         <v>25</v>
@@ -46191,22 +46203,22 @@
         <v>95</v>
       </c>
       <c r="E1133" s="4" t="s">
-        <v>172</v>
+        <v>293</v>
       </c>
       <c r="F1133" s="4">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G1133" s="4" t="s">
         <v>23</v>
       </c>
       <c r="H1133" s="4">
-        <v>3.58</v>
+        <v>138.6</v>
       </c>
       <c r="I1133" s="4" t="s">
         <v>24</v>
       </c>
       <c r="J1133" s="4">
-        <v>25.06</v>
+        <v>138.6</v>
       </c>
       <c r="K1133" s="4" t="s">
         <v>25</v>
@@ -46229,22 +46241,22 @@
         <v>95</v>
       </c>
       <c r="E1134" s="4" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="F1134" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1134" s="4" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="H1134" s="4">
-        <v>138.6</v>
+        <v>3.2</v>
       </c>
       <c r="I1134" s="4" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="J1134" s="4">
-        <v>138.6</v>
+        <v>6.4</v>
       </c>
       <c r="K1134" s="4" t="s">
         <v>25</v>
@@ -46264,25 +46276,25 @@
         <v>14</v>
       </c>
       <c r="D1135" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E1135" s="4" t="s">
-        <v>294</v>
+        <v>145</v>
+      </c>
+      <c r="E1135" s="5" t="s">
+        <v>281</v>
       </c>
       <c r="F1135" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G1135" s="4" t="s">
-        <v>44</v>
+        <v>210</v>
       </c>
       <c r="H1135" s="4">
-        <v>3.2</v>
+        <v>101</v>
       </c>
       <c r="I1135" s="4" t="s">
-        <v>45</v>
+        <v>211</v>
       </c>
       <c r="J1135" s="4">
-        <v>6.4</v>
+        <v>606</v>
       </c>
       <c r="K1135" s="4" t="s">
         <v>25</v>
@@ -46304,23 +46316,23 @@
       <c r="D1136" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="E1136" s="5" t="s">
-        <v>281</v>
+      <c r="E1136" s="4" t="s">
+        <v>280</v>
       </c>
       <c r="F1136" s="4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G1136" s="4" t="s">
-        <v>210</v>
+        <v>23</v>
       </c>
       <c r="H1136" s="4">
-        <v>101</v>
+        <v>12.56</v>
       </c>
       <c r="I1136" s="4" t="s">
-        <v>211</v>
+        <v>24</v>
       </c>
       <c r="J1136" s="4">
-        <v>606</v>
+        <v>100.48</v>
       </c>
       <c r="K1136" s="4" t="s">
         <v>25</v>
@@ -46340,68 +46352,30 @@
         <v>14</v>
       </c>
       <c r="D1137" s="4" t="s">
-        <v>145</v>
+        <v>97</v>
       </c>
       <c r="E1137" s="4" t="s">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="F1137" s="4">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G1137" s="4" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="H1137" s="4">
-        <v>12.56</v>
+        <v>26</v>
       </c>
       <c r="I1137" s="4" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="J1137" s="4">
-        <v>100.48</v>
+        <v>26</v>
       </c>
       <c r="K1137" s="4" t="s">
         <v>25</v>
       </c>
       <c r="L1137" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="1138" spans="1:12">
-      <c r="A1138" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="B1138" s="6">
-        <v>46121</v>
-      </c>
-      <c r="C1138" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D1138" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="E1138" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="F1138" s="4">
-        <v>1</v>
-      </c>
-      <c r="G1138" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="H1138" s="4">
-        <v>26</v>
-      </c>
-      <c r="I1138" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="J1138" s="4">
-        <v>26</v>
-      </c>
-      <c r="K1138" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="L1138" s="4" t="s">
         <v>20</v>
       </c>
     </row>
